--- a/coincidencias_comisiones.xlsx
+++ b/coincidencias_comisiones.xlsx
@@ -5,16 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/044771503088af63/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vicel\Proyectos\constitutional-proposal-tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="685" documentId="8_{4C345CB1-7C1D-49F0-8F7F-9A802A662A77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A2AE0F0-A710-4C4C-AE53-83882820C48F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E3189F-B805-41F1-97BD-EAF034DA85AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="10980" windowHeight="13770" activeTab="1" xr2:uid="{EB1ABC4A-685D-416C-81A4-F83CAA4FCE57}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" activeTab="2" xr2:uid="{EB1ABC4A-685D-416C-81A4-F83CAA4FCE57}"/>
   </bookViews>
   <sheets>
     <sheet name="Comisión 1" sheetId="1" r:id="rId1"/>
     <sheet name="Comisión 3" sheetId="2" r:id="rId2"/>
+    <sheet name="Comisión 6" sheetId="3" r:id="rId3"/>
+    <sheet name="Comisión 5" sheetId="4" r:id="rId4"/>
+    <sheet name="Comisión 7" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comisión 1'!$A$1:$G$1</definedName>
@@ -41,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="269">
   <si>
     <t>Número previo</t>
   </si>
@@ -704,13 +707,157 @@
   </si>
   <si>
     <t>C3-GEN-CH01-ART29</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART1</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART2</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART4</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART5</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART6</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART7</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART9</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART10</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART11</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART12</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART15</t>
+  </si>
+  <si>
+    <t>Una palabra de diferencia</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART18</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART18A</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART21</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART22</t>
+  </si>
+  <si>
+    <t>C6_IND02-08_ART16</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART24</t>
+  </si>
+  <si>
+    <t>Sobra un inciso</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART25</t>
+  </si>
+  <si>
+    <t>C6_IND03-07_ART3</t>
+  </si>
+  <si>
+    <t>C6_IND03-07_ART4</t>
+  </si>
+  <si>
+    <t>C6_IND03-07_ART5</t>
+  </si>
+  <si>
+    <t>C6_IND03-07_ART6</t>
+  </si>
+  <si>
+    <t>C6_IND03-07_ART7</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART29</t>
+  </si>
+  <si>
+    <t>C6_IND03-07_ART9</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART30</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART34</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART37</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART41</t>
+  </si>
+  <si>
+    <t>C6_IND03-07_ART16</t>
+  </si>
+  <si>
+    <t>C6_X_ART24</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART45</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART46</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART47</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART48</t>
+  </si>
+  <si>
+    <t>Sobran dos incisos</t>
+  </si>
+  <si>
+    <t>C6_X_ART28B</t>
+  </si>
+  <si>
+    <t>C6_X_ART42</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART64</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART66</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART67</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART69</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART70</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART73</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART74A</t>
+  </si>
+  <si>
+    <t>C6_GEN1_ART77</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -729,6 +876,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FFA31515"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -751,9 +904,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3980,4 +4136,1511 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5520BB1-FD64-4562-8A4D-B7ECF35F2484}">
+  <dimension ref="A1:G120"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>339</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>340</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>341</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>342</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>343</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>344</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>345</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>346</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>347</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>348</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>349</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E12" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>350</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>351</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>352</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>353</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>354</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>355</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E18" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>356</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>357</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>358</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>359</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>360</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>361</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>362</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>363</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>4</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>364</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>365</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E28" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>366</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>4</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>367</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
+        <v>4</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>368</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>369</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>370</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>371</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34" t="s">
+        <v>4</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>372</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35" t="s">
+        <v>4</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>373</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
+        <v>2</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E36" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>374</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>375</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>376</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39" t="s">
+        <v>4</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>377</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s">
+        <v>4</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>378</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41" t="s">
+        <v>4</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>379</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42" t="s">
+        <v>4</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>380</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s">
+        <v>4</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>381</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>382</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45" t="s">
+        <v>4</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>383</v>
+      </c>
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46" t="s">
+        <v>4</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>384</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>385</v>
+      </c>
+      <c r="B48">
+        <v>1</v>
+      </c>
+      <c r="C48" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>386</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>387</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>388</v>
+      </c>
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>389</v>
+      </c>
+      <c r="B52">
+        <v>1</v>
+      </c>
+      <c r="C52" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>390</v>
+      </c>
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="C53" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>391</v>
+      </c>
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>392</v>
+      </c>
+      <c r="B55">
+        <v>1</v>
+      </c>
+      <c r="C55" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>393</v>
+      </c>
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="C56" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>394</v>
+      </c>
+      <c r="B57">
+        <v>1</v>
+      </c>
+      <c r="C57" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>395</v>
+      </c>
+      <c r="B58">
+        <v>1</v>
+      </c>
+      <c r="C58" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>396</v>
+      </c>
+      <c r="B59">
+        <v>1</v>
+      </c>
+      <c r="C59" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>397</v>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="C60" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>398</v>
+      </c>
+      <c r="B61">
+        <v>1</v>
+      </c>
+      <c r="C61" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>399</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>400</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
+      </c>
+      <c r="C63" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>401</v>
+      </c>
+      <c r="B64">
+        <v>1</v>
+      </c>
+      <c r="C64" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>402</v>
+      </c>
+      <c r="B65">
+        <v>1</v>
+      </c>
+      <c r="C65" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>403</v>
+      </c>
+      <c r="B66">
+        <v>1</v>
+      </c>
+      <c r="C66" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>404</v>
+      </c>
+      <c r="B67">
+        <v>1</v>
+      </c>
+      <c r="C67" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>405</v>
+      </c>
+      <c r="B68">
+        <v>1</v>
+      </c>
+      <c r="C68" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>406</v>
+      </c>
+      <c r="B69">
+        <v>1</v>
+      </c>
+      <c r="C69" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>407</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
+      </c>
+      <c r="C70" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>408</v>
+      </c>
+      <c r="B71">
+        <v>1</v>
+      </c>
+      <c r="C71" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>409</v>
+      </c>
+      <c r="B72">
+        <v>1</v>
+      </c>
+      <c r="C72" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>410</v>
+      </c>
+      <c r="B73">
+        <v>1</v>
+      </c>
+      <c r="C73" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>411</v>
+      </c>
+      <c r="B74">
+        <v>1</v>
+      </c>
+      <c r="C74" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>412</v>
+      </c>
+      <c r="B75">
+        <v>1</v>
+      </c>
+      <c r="C75" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>413</v>
+      </c>
+      <c r="B76">
+        <v>1</v>
+      </c>
+      <c r="C76" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>414</v>
+      </c>
+      <c r="B77">
+        <v>1</v>
+      </c>
+      <c r="C77" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>415</v>
+      </c>
+      <c r="B78">
+        <v>1</v>
+      </c>
+      <c r="C78" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>416</v>
+      </c>
+      <c r="B79">
+        <v>1</v>
+      </c>
+      <c r="C79" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>417</v>
+      </c>
+      <c r="B80">
+        <v>1</v>
+      </c>
+      <c r="C80" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>418</v>
+      </c>
+      <c r="B81">
+        <v>1</v>
+      </c>
+      <c r="C81" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>419</v>
+      </c>
+      <c r="B82">
+        <v>1</v>
+      </c>
+      <c r="C82" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>420</v>
+      </c>
+      <c r="B83">
+        <v>1</v>
+      </c>
+      <c r="C83" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>421</v>
+      </c>
+      <c r="B84">
+        <v>1</v>
+      </c>
+      <c r="C84" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>422</v>
+      </c>
+      <c r="B85">
+        <v>1</v>
+      </c>
+      <c r="C85" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>423</v>
+      </c>
+      <c r="B86">
+        <v>1</v>
+      </c>
+      <c r="C86" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>424</v>
+      </c>
+      <c r="B87">
+        <v>1</v>
+      </c>
+      <c r="C87" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>425</v>
+      </c>
+      <c r="B88">
+        <v>1</v>
+      </c>
+      <c r="C88" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>426</v>
+      </c>
+      <c r="B89">
+        <v>1</v>
+      </c>
+      <c r="C89" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>427</v>
+      </c>
+      <c r="B90">
+        <v>1</v>
+      </c>
+      <c r="C90" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>428</v>
+      </c>
+      <c r="B91">
+        <v>1</v>
+      </c>
+      <c r="C91" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <v>429</v>
+      </c>
+      <c r="B92">
+        <v>1</v>
+      </c>
+      <c r="C92" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <v>430</v>
+      </c>
+      <c r="B93">
+        <v>1</v>
+      </c>
+      <c r="C93" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A94">
+        <v>431</v>
+      </c>
+      <c r="B94">
+        <v>1</v>
+      </c>
+      <c r="C94" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <v>432</v>
+      </c>
+      <c r="B95">
+        <v>1</v>
+      </c>
+      <c r="C95" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <v>433</v>
+      </c>
+      <c r="B96">
+        <v>1</v>
+      </c>
+      <c r="C96" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <v>434</v>
+      </c>
+      <c r="B97">
+        <v>1</v>
+      </c>
+      <c r="C97" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <v>435</v>
+      </c>
+      <c r="B98">
+        <v>1</v>
+      </c>
+      <c r="C98" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>436</v>
+      </c>
+      <c r="B99">
+        <v>1</v>
+      </c>
+      <c r="C99" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <v>437</v>
+      </c>
+      <c r="B100">
+        <v>1</v>
+      </c>
+      <c r="C100" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>438</v>
+      </c>
+      <c r="B101">
+        <v>1</v>
+      </c>
+      <c r="C101" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <v>439</v>
+      </c>
+      <c r="B102">
+        <v>1</v>
+      </c>
+      <c r="C102" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>440</v>
+      </c>
+      <c r="B103">
+        <v>1</v>
+      </c>
+      <c r="C103" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A104">
+        <v>441</v>
+      </c>
+      <c r="B104">
+        <v>1</v>
+      </c>
+      <c r="C104" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <v>442</v>
+      </c>
+      <c r="B105">
+        <v>1</v>
+      </c>
+      <c r="C105" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A106">
+        <v>443</v>
+      </c>
+      <c r="B106">
+        <v>1</v>
+      </c>
+      <c r="C106" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A107">
+        <v>444</v>
+      </c>
+      <c r="B107">
+        <v>1</v>
+      </c>
+      <c r="C107" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A108">
+        <v>445</v>
+      </c>
+      <c r="B108">
+        <v>1</v>
+      </c>
+      <c r="C108" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A109">
+        <v>446</v>
+      </c>
+      <c r="B109">
+        <v>1</v>
+      </c>
+      <c r="C109" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A110">
+        <v>447</v>
+      </c>
+      <c r="B110">
+        <v>1</v>
+      </c>
+      <c r="C110" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A111">
+        <v>448</v>
+      </c>
+      <c r="B111">
+        <v>1</v>
+      </c>
+      <c r="C111" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A112">
+        <v>449</v>
+      </c>
+      <c r="B112">
+        <v>1</v>
+      </c>
+      <c r="C112" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A113">
+        <v>450</v>
+      </c>
+      <c r="B113">
+        <v>1</v>
+      </c>
+      <c r="C113" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A114">
+        <v>451</v>
+      </c>
+      <c r="B114">
+        <v>1</v>
+      </c>
+      <c r="C114" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A115">
+        <v>452</v>
+      </c>
+      <c r="B115">
+        <v>1</v>
+      </c>
+      <c r="C115" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A116">
+        <v>453</v>
+      </c>
+      <c r="B116">
+        <v>1</v>
+      </c>
+      <c r="C116" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A117">
+        <v>454</v>
+      </c>
+      <c r="B117">
+        <v>1</v>
+      </c>
+      <c r="C117" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A118">
+        <v>455</v>
+      </c>
+      <c r="B118">
+        <v>1</v>
+      </c>
+      <c r="C118" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A119">
+        <v>456</v>
+      </c>
+      <c r="B119">
+        <v>1</v>
+      </c>
+      <c r="C119" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A120">
+        <v>457</v>
+      </c>
+      <c r="B120">
+        <v>1</v>
+      </c>
+      <c r="C120" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF016F2B-E88B-426D-8061-4E20A3875DD7}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C625EF6D-2FED-45E6-AF0C-2B30004BDDFE}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/coincidencias_comisiones.xlsx
+++ b/coincidencias_comisiones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vicel\Proyectos\constitutional-proposal-tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E3189F-B805-41F1-97BD-EAF034DA85AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB0EA444-BD9F-4C49-A0EC-5EDD919F1D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" activeTab="2" xr2:uid="{EB1ABC4A-685D-416C-81A4-F83CAA4FCE57}"/>
   </bookViews>
@@ -22,6 +22,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comisión 1'!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comisión 3'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Comisión 6'!$A$1:$G$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="345">
   <si>
     <t>Número previo</t>
   </si>
@@ -851,6 +852,234 @@
   </si>
   <si>
     <t>C6_GEN1_ART77</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART1</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART3</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART8</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART9</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART10</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART10A</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART11</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART13</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART14</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART17</t>
+  </si>
+  <si>
+    <t>C6_IND05-08_ART12BIS</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART19</t>
+  </si>
+  <si>
+    <t>C6_IND05-08_ART13BIS</t>
+  </si>
+  <si>
+    <t>C6_IND05-08_ART13TER</t>
+  </si>
+  <si>
+    <t>C6_IND04-01-2_ART15</t>
+  </si>
+  <si>
+    <t>C6_IND04-01-2_ART16</t>
+  </si>
+  <si>
+    <t>C6_IND04-27_ART17</t>
+  </si>
+  <si>
+    <t>C6_IND04-27_ART18</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART22</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART24</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART25</t>
+  </si>
+  <si>
+    <t>Una coma de diferencia</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART27</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART34</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART36A</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART37</t>
+  </si>
+  <si>
+    <t>C6_IND04-27_ART29</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART41</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART42</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART43</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART56A</t>
+  </si>
+  <si>
+    <t>C6_IND05-08_ART35BIS</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART61</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART62</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART62C</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART63A</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART64</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART65C</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART69</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART70</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART73B</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART74</t>
+  </si>
+  <si>
+    <t>"de la Contraloría" sobra</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART75</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART76</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART77</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART78</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART82</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART87</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART88</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART91</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART101</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART89</t>
+  </si>
+  <si>
+    <t>Una letra de diferencia</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART114</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART108</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART116</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART117A</t>
+  </si>
+  <si>
+    <t>C6_IND05-08_ART68BIS</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART118A</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART119</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART127</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART129</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART130</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART131</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART136</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART137</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART138</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART140</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART141</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART142</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART145</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART148</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART149</t>
+  </si>
+  <si>
+    <t>C6_GEN3_ART150</t>
+  </si>
+  <si>
+    <t>C6_IND05-08_ARTN90</t>
   </si>
 </sst>
 </file>
@@ -4196,21 +4425,21 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -4219,12 +4448,12 @@
         <v>4</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -4233,12 +4462,12 @@
         <v>4</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -4247,12 +4476,12 @@
         <v>4</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -4261,12 +4490,12 @@
         <v>4</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -4275,12 +4504,12 @@
         <v>4</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -4289,12 +4518,12 @@
         <v>4</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -4303,43 +4532,40 @@
         <v>4</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E12" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>4</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="E13" t="s">
-        <v>150</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -4348,12 +4574,12 @@
         <v>4</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -4362,12 +4588,12 @@
         <v>4</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -4376,12 +4602,12 @@
         <v>4</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -4390,1239 +4616,1502 @@
         <v>4</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
+        <v>359</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>360</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>361</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>362</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>363</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>364</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>366</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>367</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>368</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>4</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>369</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>371</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>372</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>4</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>374</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
+        <v>4</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>375</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>376</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>377</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>378</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34" t="s">
+        <v>4</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>379</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35" t="s">
+        <v>4</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>380</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
+        <v>4</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>381</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>382</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>383</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39" t="s">
+        <v>4</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>384</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s">
+        <v>4</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>385</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41" t="s">
+        <v>4</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>387</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42" t="s">
+        <v>4</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>388</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s">
+        <v>4</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>389</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>390</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45" t="s">
+        <v>4</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>391</v>
+      </c>
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46" t="s">
+        <v>4</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>392</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s">
+        <v>4</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>393</v>
+      </c>
+      <c r="B48">
+        <v>1</v>
+      </c>
+      <c r="C48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>394</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49" t="s">
+        <v>4</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>395</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>396</v>
+      </c>
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51" t="s">
+        <v>4</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>397</v>
+      </c>
+      <c r="B52">
+        <v>1</v>
+      </c>
+      <c r="C52" t="s">
+        <v>4</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>398</v>
+      </c>
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="C53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>399</v>
+      </c>
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54" t="s">
+        <v>4</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>400</v>
+      </c>
+      <c r="B55">
+        <v>1</v>
+      </c>
+      <c r="C55" t="s">
+        <v>4</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>401</v>
+      </c>
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="C56" t="s">
+        <v>4</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>402</v>
+      </c>
+      <c r="B57">
+        <v>1</v>
+      </c>
+      <c r="C57" t="s">
+        <v>4</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>403</v>
+      </c>
+      <c r="B58">
+        <v>1</v>
+      </c>
+      <c r="C58" t="s">
+        <v>4</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>404</v>
+      </c>
+      <c r="B59">
+        <v>1</v>
+      </c>
+      <c r="C59" t="s">
+        <v>4</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>406</v>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="C60" t="s">
+        <v>4</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>407</v>
+      </c>
+      <c r="B61">
+        <v>1</v>
+      </c>
+      <c r="C61" t="s">
+        <v>4</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>408</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62" t="s">
+        <v>4</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>409</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
+      </c>
+      <c r="C63" t="s">
+        <v>4</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>410</v>
+      </c>
+      <c r="B64">
+        <v>1</v>
+      </c>
+      <c r="C64" t="s">
+        <v>4</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>411</v>
+      </c>
+      <c r="B65">
+        <v>1</v>
+      </c>
+      <c r="C65" t="s">
+        <v>4</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>412</v>
+      </c>
+      <c r="B66">
+        <v>1</v>
+      </c>
+      <c r="C66" t="s">
+        <v>4</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>413</v>
+      </c>
+      <c r="B67">
+        <v>1</v>
+      </c>
+      <c r="C67" t="s">
+        <v>4</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>414</v>
+      </c>
+      <c r="B68">
+        <v>1</v>
+      </c>
+      <c r="C68" t="s">
+        <v>4</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>415</v>
+      </c>
+      <c r="B69">
+        <v>1</v>
+      </c>
+      <c r="C69" t="s">
+        <v>4</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>416</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
+      </c>
+      <c r="C70" t="s">
+        <v>4</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>417</v>
+      </c>
+      <c r="B71">
+        <v>1</v>
+      </c>
+      <c r="C71" t="s">
+        <v>4</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>418</v>
+      </c>
+      <c r="B72">
+        <v>1</v>
+      </c>
+      <c r="C72" t="s">
+        <v>4</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>419</v>
+      </c>
+      <c r="B73">
+        <v>1</v>
+      </c>
+      <c r="C73" t="s">
+        <v>4</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>420</v>
+      </c>
+      <c r="B74">
+        <v>1</v>
+      </c>
+      <c r="C74" t="s">
+        <v>4</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>421</v>
+      </c>
+      <c r="B75">
+        <v>1</v>
+      </c>
+      <c r="C75" t="s">
+        <v>4</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>422</v>
+      </c>
+      <c r="B76">
+        <v>1</v>
+      </c>
+      <c r="C76" t="s">
+        <v>4</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>423</v>
+      </c>
+      <c r="B77">
+        <v>1</v>
+      </c>
+      <c r="C77" t="s">
+        <v>4</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>424</v>
+      </c>
+      <c r="B78">
+        <v>1</v>
+      </c>
+      <c r="C78" t="s">
+        <v>4</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>426</v>
+      </c>
+      <c r="B79">
+        <v>1</v>
+      </c>
+      <c r="C79" t="s">
+        <v>4</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>427</v>
+      </c>
+      <c r="B80">
+        <v>1</v>
+      </c>
+      <c r="C80" t="s">
+        <v>4</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>428</v>
+      </c>
+      <c r="B81">
+        <v>1</v>
+      </c>
+      <c r="C81" t="s">
+        <v>4</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>429</v>
+      </c>
+      <c r="B82">
+        <v>1</v>
+      </c>
+      <c r="C82" t="s">
+        <v>4</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>431</v>
+      </c>
+      <c r="B83">
+        <v>1</v>
+      </c>
+      <c r="C83" t="s">
+        <v>4</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>432</v>
+      </c>
+      <c r="B84">
+        <v>1</v>
+      </c>
+      <c r="C84" t="s">
+        <v>4</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>435</v>
+      </c>
+      <c r="B85">
+        <v>1</v>
+      </c>
+      <c r="C85" t="s">
+        <v>4</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>436</v>
+      </c>
+      <c r="B86">
+        <v>1</v>
+      </c>
+      <c r="C86" t="s">
+        <v>4</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>438</v>
+      </c>
+      <c r="B87">
+        <v>1</v>
+      </c>
+      <c r="C87" t="s">
+        <v>4</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>439</v>
+      </c>
+      <c r="B88">
+        <v>1</v>
+      </c>
+      <c r="C88" t="s">
+        <v>4</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>440</v>
+      </c>
+      <c r="B89">
+        <v>1</v>
+      </c>
+      <c r="C89" t="s">
+        <v>4</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>442</v>
+      </c>
+      <c r="B90">
+        <v>1</v>
+      </c>
+      <c r="C90" t="s">
+        <v>4</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>443</v>
+      </c>
+      <c r="B91">
+        <v>1</v>
+      </c>
+      <c r="C91" t="s">
+        <v>4</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <v>444</v>
+      </c>
+      <c r="B92">
+        <v>1</v>
+      </c>
+      <c r="C92" t="s">
+        <v>4</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <v>445</v>
+      </c>
+      <c r="B93">
+        <v>1</v>
+      </c>
+      <c r="C93" t="s">
+        <v>4</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A94">
+        <v>446</v>
+      </c>
+      <c r="B94">
+        <v>1</v>
+      </c>
+      <c r="C94" t="s">
+        <v>4</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <v>448</v>
+      </c>
+      <c r="B95">
+        <v>1</v>
+      </c>
+      <c r="C95" t="s">
+        <v>4</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <v>450</v>
+      </c>
+      <c r="B96">
+        <v>1</v>
+      </c>
+      <c r="C96" t="s">
+        <v>4</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <v>452</v>
+      </c>
+      <c r="B97">
+        <v>1</v>
+      </c>
+      <c r="C97" t="s">
+        <v>4</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <v>454</v>
+      </c>
+      <c r="B98">
+        <v>1</v>
+      </c>
+      <c r="C98" t="s">
+        <v>4</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="E98" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>455</v>
+      </c>
+      <c r="B99">
+        <v>1</v>
+      </c>
+      <c r="C99" t="s">
+        <v>4</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <v>456</v>
+      </c>
+      <c r="B100">
+        <v>1</v>
+      </c>
+      <c r="C100" t="s">
+        <v>4</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>457</v>
+      </c>
+      <c r="B101">
+        <v>1</v>
+      </c>
+      <c r="C101" t="s">
+        <v>4</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <v>341</v>
+      </c>
+      <c r="B102">
+        <v>1</v>
+      </c>
+      <c r="C102" t="s">
+        <v>2</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>349</v>
+      </c>
+      <c r="B103">
+        <v>1</v>
+      </c>
+      <c r="C103" t="s">
+        <v>2</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E103" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A104">
         <v>355</v>
       </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18" t="s">
-        <v>2</v>
-      </c>
-      <c r="D18" s="2" t="s">
+      <c r="B104">
+        <v>1</v>
+      </c>
+      <c r="C104" t="s">
+        <v>2</v>
+      </c>
+      <c r="D104" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E104" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <v>356</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20">
-        <v>357</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21">
-        <v>358</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22">
-        <v>359</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23">
-        <v>360</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24">
-        <v>361</v>
-      </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25">
-        <v>362</v>
-      </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25" t="s">
-        <v>4</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26">
-        <v>363</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26" t="s">
-        <v>4</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27">
-        <v>364</v>
-      </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27" t="s">
-        <v>4</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A105">
         <v>365</v>
       </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28" t="s">
-        <v>2</v>
-      </c>
-      <c r="D28" s="2" t="s">
+      <c r="B105">
+        <v>1</v>
+      </c>
+      <c r="C105" t="s">
+        <v>2</v>
+      </c>
+      <c r="D105" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E105" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29">
-        <v>366</v>
-      </c>
-      <c r="B29">
-        <v>1</v>
-      </c>
-      <c r="C29" t="s">
-        <v>4</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30">
-        <v>367</v>
-      </c>
-      <c r="B30">
-        <v>1</v>
-      </c>
-      <c r="C30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31">
-        <v>368</v>
-      </c>
-      <c r="B31">
-        <v>1</v>
-      </c>
-      <c r="C31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32">
-        <v>369</v>
-      </c>
-      <c r="B32">
-        <v>1</v>
-      </c>
-      <c r="C32" t="s">
-        <v>4</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A106">
         <v>370</v>
       </c>
-      <c r="B33">
-        <v>1</v>
-      </c>
-      <c r="C33" t="s">
-        <v>2</v>
-      </c>
-      <c r="D33" s="2" t="s">
+      <c r="B106">
+        <v>1</v>
+      </c>
+      <c r="C106" t="s">
+        <v>2</v>
+      </c>
+      <c r="D106" s="2" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A34">
-        <v>371</v>
-      </c>
-      <c r="B34">
-        <v>1</v>
-      </c>
-      <c r="C34" t="s">
-        <v>4</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A35">
-        <v>372</v>
-      </c>
-      <c r="B35">
-        <v>1</v>
-      </c>
-      <c r="C35" t="s">
-        <v>4</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A36">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A107">
         <v>373</v>
       </c>
-      <c r="B36">
-        <v>1</v>
-      </c>
-      <c r="C36" t="s">
-        <v>2</v>
-      </c>
-      <c r="D36" s="2" t="s">
+      <c r="B107">
+        <v>1</v>
+      </c>
+      <c r="C107" t="s">
+        <v>2</v>
+      </c>
+      <c r="D107" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E107" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A37">
-        <v>374</v>
-      </c>
-      <c r="B37">
-        <v>1</v>
-      </c>
-      <c r="C37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A38">
-        <v>375</v>
-      </c>
-      <c r="B38">
-        <v>1</v>
-      </c>
-      <c r="C38" t="s">
-        <v>4</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A39">
-        <v>376</v>
-      </c>
-      <c r="B39">
-        <v>1</v>
-      </c>
-      <c r="C39" t="s">
-        <v>4</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A40">
-        <v>377</v>
-      </c>
-      <c r="B40">
-        <v>1</v>
-      </c>
-      <c r="C40" t="s">
-        <v>4</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A41">
-        <v>378</v>
-      </c>
-      <c r="B41">
-        <v>1</v>
-      </c>
-      <c r="C41" t="s">
-        <v>4</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A42">
-        <v>379</v>
-      </c>
-      <c r="B42">
-        <v>1</v>
-      </c>
-      <c r="C42" t="s">
-        <v>4</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A43">
-        <v>380</v>
-      </c>
-      <c r="B43">
-        <v>1</v>
-      </c>
-      <c r="C43" t="s">
-        <v>4</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A44">
-        <v>381</v>
-      </c>
-      <c r="B44">
-        <v>1</v>
-      </c>
-      <c r="C44" t="s">
-        <v>4</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A45">
-        <v>382</v>
-      </c>
-      <c r="B45">
-        <v>1</v>
-      </c>
-      <c r="C45" t="s">
-        <v>4</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A46">
-        <v>383</v>
-      </c>
-      <c r="B46">
-        <v>1</v>
-      </c>
-      <c r="C46" t="s">
-        <v>4</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A47">
-        <v>384</v>
-      </c>
-      <c r="B47">
-        <v>1</v>
-      </c>
-      <c r="C47" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A48">
-        <v>385</v>
-      </c>
-      <c r="B48">
-        <v>1</v>
-      </c>
-      <c r="C48" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A49">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A108">
         <v>386</v>
       </c>
-      <c r="B49">
-        <v>1</v>
-      </c>
-      <c r="C49" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50">
-        <v>387</v>
-      </c>
-      <c r="B50">
-        <v>1</v>
-      </c>
-      <c r="C50" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51">
-        <v>388</v>
-      </c>
-      <c r="B51">
-        <v>1</v>
-      </c>
-      <c r="C51" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52">
-        <v>389</v>
-      </c>
-      <c r="B52">
-        <v>1</v>
-      </c>
-      <c r="C52" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53">
-        <v>390</v>
-      </c>
-      <c r="B53">
-        <v>1</v>
-      </c>
-      <c r="C53" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A54">
-        <v>391</v>
-      </c>
-      <c r="B54">
-        <v>1</v>
-      </c>
-      <c r="C54" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A55">
-        <v>392</v>
-      </c>
-      <c r="B55">
-        <v>1</v>
-      </c>
-      <c r="C55" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56">
-        <v>393</v>
-      </c>
-      <c r="B56">
-        <v>1</v>
-      </c>
-      <c r="C56" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57">
-        <v>394</v>
-      </c>
-      <c r="B57">
-        <v>1</v>
-      </c>
-      <c r="C57" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A58">
-        <v>395</v>
-      </c>
-      <c r="B58">
-        <v>1</v>
-      </c>
-      <c r="C58" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A59">
-        <v>396</v>
-      </c>
-      <c r="B59">
-        <v>1</v>
-      </c>
-      <c r="C59" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A60">
-        <v>397</v>
-      </c>
-      <c r="B60">
-        <v>1</v>
-      </c>
-      <c r="C60" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A61">
-        <v>398</v>
-      </c>
-      <c r="B61">
-        <v>1</v>
-      </c>
-      <c r="C61" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A62">
-        <v>399</v>
-      </c>
-      <c r="B62">
-        <v>1</v>
-      </c>
-      <c r="C62" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A63">
-        <v>400</v>
-      </c>
-      <c r="B63">
-        <v>1</v>
-      </c>
-      <c r="C63" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A64">
-        <v>401</v>
-      </c>
-      <c r="B64">
-        <v>1</v>
-      </c>
-      <c r="C64" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A65">
-        <v>402</v>
-      </c>
-      <c r="B65">
-        <v>1</v>
-      </c>
-      <c r="C65" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A66">
-        <v>403</v>
-      </c>
-      <c r="B66">
-        <v>1</v>
-      </c>
-      <c r="C66" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A67">
-        <v>404</v>
-      </c>
-      <c r="B67">
-        <v>1</v>
-      </c>
-      <c r="C67" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A68">
+      <c r="B108">
+        <v>1</v>
+      </c>
+      <c r="C108" t="s">
+        <v>2</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E108" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A109">
         <v>405</v>
       </c>
-      <c r="B68">
-        <v>1</v>
-      </c>
-      <c r="C68" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A69">
-        <v>406</v>
-      </c>
-      <c r="B69">
-        <v>1</v>
-      </c>
-      <c r="C69" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A70">
-        <v>407</v>
-      </c>
-      <c r="B70">
-        <v>1</v>
-      </c>
-      <c r="C70" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A71">
-        <v>408</v>
-      </c>
-      <c r="B71">
-        <v>1</v>
-      </c>
-      <c r="C71" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A72">
-        <v>409</v>
-      </c>
-      <c r="B72">
-        <v>1</v>
-      </c>
-      <c r="C72" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A73">
-        <v>410</v>
-      </c>
-      <c r="B73">
-        <v>1</v>
-      </c>
-      <c r="C73" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A74">
-        <v>411</v>
-      </c>
-      <c r="B74">
-        <v>1</v>
-      </c>
-      <c r="C74" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A75">
-        <v>412</v>
-      </c>
-      <c r="B75">
-        <v>1</v>
-      </c>
-      <c r="C75" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A76">
-        <v>413</v>
-      </c>
-      <c r="B76">
-        <v>1</v>
-      </c>
-      <c r="C76" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A77">
-        <v>414</v>
-      </c>
-      <c r="B77">
-        <v>1</v>
-      </c>
-      <c r="C77" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A78">
-        <v>415</v>
-      </c>
-      <c r="B78">
-        <v>1</v>
-      </c>
-      <c r="C78" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A79">
-        <v>416</v>
-      </c>
-      <c r="B79">
-        <v>1</v>
-      </c>
-      <c r="C79" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A80">
-        <v>417</v>
-      </c>
-      <c r="B80">
-        <v>1</v>
-      </c>
-      <c r="C80" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A81">
-        <v>418</v>
-      </c>
-      <c r="B81">
-        <v>1</v>
-      </c>
-      <c r="C81" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A82">
-        <v>419</v>
-      </c>
-      <c r="B82">
-        <v>1</v>
-      </c>
-      <c r="C82" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A83">
-        <v>420</v>
-      </c>
-      <c r="B83">
-        <v>1</v>
-      </c>
-      <c r="C83" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A84">
-        <v>421</v>
-      </c>
-      <c r="B84">
-        <v>1</v>
-      </c>
-      <c r="C84" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A85">
-        <v>422</v>
-      </c>
-      <c r="B85">
-        <v>1</v>
-      </c>
-      <c r="C85" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A86">
-        <v>423</v>
-      </c>
-      <c r="B86">
-        <v>1</v>
-      </c>
-      <c r="C86" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A87">
-        <v>424</v>
-      </c>
-      <c r="B87">
-        <v>1</v>
-      </c>
-      <c r="C87" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A88">
+      <c r="B109">
+        <v>1</v>
+      </c>
+      <c r="C109" t="s">
+        <v>2</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E109" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A110">
         <v>425</v>
       </c>
-      <c r="B88">
-        <v>1</v>
-      </c>
-      <c r="C88" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A89">
-        <v>426</v>
-      </c>
-      <c r="B89">
-        <v>1</v>
-      </c>
-      <c r="C89" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A90">
-        <v>427</v>
-      </c>
-      <c r="B90">
-        <v>1</v>
-      </c>
-      <c r="C90" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A91">
-        <v>428</v>
-      </c>
-      <c r="B91">
-        <v>1</v>
-      </c>
-      <c r="C91" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A92">
-        <v>429</v>
-      </c>
-      <c r="B92">
-        <v>1</v>
-      </c>
-      <c r="C92" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A93">
+      <c r="B110">
+        <v>1</v>
+      </c>
+      <c r="C110" t="s">
+        <v>2</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E110" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A111">
         <v>430</v>
       </c>
-      <c r="B93">
-        <v>1</v>
-      </c>
-      <c r="C93" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A94">
-        <v>431</v>
-      </c>
-      <c r="B94">
-        <v>1</v>
-      </c>
-      <c r="C94" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A95">
-        <v>432</v>
-      </c>
-      <c r="B95">
-        <v>1</v>
-      </c>
-      <c r="C95" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A96">
+      <c r="B111">
+        <v>1</v>
+      </c>
+      <c r="C111" t="s">
+        <v>2</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E111" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A112">
         <v>433</v>
       </c>
-      <c r="B96">
-        <v>1</v>
-      </c>
-      <c r="C96" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A97">
+      <c r="B112">
+        <v>1</v>
+      </c>
+      <c r="C112" t="s">
+        <v>2</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E112" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A113">
         <v>434</v>
       </c>
-      <c r="B97">
-        <v>1</v>
-      </c>
-      <c r="C97" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A98">
-        <v>435</v>
-      </c>
-      <c r="B98">
-        <v>1</v>
-      </c>
-      <c r="C98" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A99">
-        <v>436</v>
-      </c>
-      <c r="B99">
-        <v>1</v>
-      </c>
-      <c r="C99" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A100">
+      <c r="B113">
+        <v>1</v>
+      </c>
+      <c r="C113" t="s">
+        <v>2</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E113" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A114">
         <v>437</v>
       </c>
-      <c r="B100">
-        <v>1</v>
-      </c>
-      <c r="C100" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A101">
-        <v>438</v>
-      </c>
-      <c r="B101">
-        <v>1</v>
-      </c>
-      <c r="C101" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A102">
-        <v>439</v>
-      </c>
-      <c r="B102">
-        <v>1</v>
-      </c>
-      <c r="C102" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A103">
-        <v>440</v>
-      </c>
-      <c r="B103">
-        <v>1</v>
-      </c>
-      <c r="C103" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A104">
+      <c r="B114">
+        <v>1</v>
+      </c>
+      <c r="C114" t="s">
+        <v>2</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E114" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A115">
         <v>441</v>
       </c>
-      <c r="B104">
-        <v>1</v>
-      </c>
-      <c r="C104" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A105">
-        <v>442</v>
-      </c>
-      <c r="B105">
-        <v>1</v>
-      </c>
-      <c r="C105" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A106">
-        <v>443</v>
-      </c>
-      <c r="B106">
-        <v>1</v>
-      </c>
-      <c r="C106" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A107">
-        <v>444</v>
-      </c>
-      <c r="B107">
-        <v>1</v>
-      </c>
-      <c r="C107" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A108">
-        <v>445</v>
-      </c>
-      <c r="B108">
-        <v>1</v>
-      </c>
-      <c r="C108" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A109">
-        <v>446</v>
-      </c>
-      <c r="B109">
-        <v>1</v>
-      </c>
-      <c r="C109" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A110">
+      <c r="B115">
+        <v>1</v>
+      </c>
+      <c r="C115" t="s">
+        <v>2</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="E115" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A116">
         <v>447</v>
       </c>
-      <c r="B110">
-        <v>1</v>
-      </c>
-      <c r="C110" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A111">
-        <v>448</v>
-      </c>
-      <c r="B111">
-        <v>1</v>
-      </c>
-      <c r="C111" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A112">
+      <c r="B116">
+        <v>1</v>
+      </c>
+      <c r="C116" t="s">
+        <v>2</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E116" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A117">
         <v>449</v>
       </c>
-      <c r="B112">
-        <v>1</v>
-      </c>
-      <c r="C112" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A113">
-        <v>450</v>
-      </c>
-      <c r="B113">
-        <v>1</v>
-      </c>
-      <c r="C113" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A114">
+      <c r="B117">
+        <v>1</v>
+      </c>
+      <c r="C117" t="s">
+        <v>2</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="E117" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A118">
         <v>451</v>
       </c>
-      <c r="B114">
-        <v>1</v>
-      </c>
-      <c r="C114" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A115">
-        <v>452</v>
-      </c>
-      <c r="B115">
-        <v>1</v>
-      </c>
-      <c r="C115" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A116">
+      <c r="B118">
+        <v>1</v>
+      </c>
+      <c r="C118" t="s">
+        <v>2</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A119">
         <v>453</v>
       </c>
-      <c r="B116">
-        <v>1</v>
-      </c>
-      <c r="C116" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A117">
-        <v>454</v>
-      </c>
-      <c r="B117">
-        <v>1</v>
-      </c>
-      <c r="C117" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A118">
-        <v>455</v>
-      </c>
-      <c r="B118">
-        <v>1</v>
-      </c>
-      <c r="C118" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A119">
-        <v>456</v>
-      </c>
       <c r="B119">
         <v>1</v>
       </c>
       <c r="C119" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120">
-        <v>457</v>
+        <v>350</v>
       </c>
       <c r="B120">
-        <v>1</v>
-      </c>
-      <c r="C120" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E120" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G1" xr:uid="{B5520BB1-FD64-4562-8A4D-B7ECF35F2484}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G120">
+      <sortCondition ref="C1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/coincidencias_comisiones.xlsx
+++ b/coincidencias_comisiones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vicel\Proyectos\constitutional-proposal-tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB0EA444-BD9F-4C49-A0EC-5EDD919F1D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274682E4-40F4-4BC3-B332-8A1DC514EBA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" activeTab="2" xr2:uid="{EB1ABC4A-685D-416C-81A4-F83CAA4FCE57}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" activeTab="4" xr2:uid="{EB1ABC4A-685D-416C-81A4-F83CAA4FCE57}"/>
   </bookViews>
   <sheets>
     <sheet name="Comisión 1" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comisión 1'!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comisión 3'!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Comisión 6'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Comisión 7'!$A$1:$G$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="388">
   <si>
     <t>Número previo</t>
   </si>
@@ -1080,6 +1081,135 @@
   </si>
   <si>
     <t>C6_IND05-08_ARTN90</t>
+  </si>
+  <si>
+    <t>C7_GEN3_ART18</t>
+  </si>
+  <si>
+    <t>C7_GEN3_ART20</t>
+  </si>
+  <si>
+    <t>C7_GEN3_ART60</t>
+  </si>
+  <si>
+    <t>C7_GEN3_ART28</t>
+  </si>
+  <si>
+    <t>C7_GEN2_CH1_ART1</t>
+  </si>
+  <si>
+    <t>C7_GEN2_CH1_ART1_2</t>
+  </si>
+  <si>
+    <t>C7_GEN2_CH1_ART3_2</t>
+  </si>
+  <si>
+    <t>C7_GEN2_ART2</t>
+  </si>
+  <si>
+    <t>Un inciso de sobra</t>
+  </si>
+  <si>
+    <t>C7_GEN2_CH1_ART4</t>
+  </si>
+  <si>
+    <t>C7_GEN2_CH2_ART1</t>
+  </si>
+  <si>
+    <t>C7_GEN2_CH2_ART3</t>
+  </si>
+  <si>
+    <t>C7_IND03-19_CH13_ART8</t>
+  </si>
+  <si>
+    <t>C7_GEN2_CH3_ART1</t>
+  </si>
+  <si>
+    <t>C7_GEN2_CH3_ART2</t>
+  </si>
+  <si>
+    <t>C7_GEN2_CH3_ART2_1</t>
+  </si>
+  <si>
+    <t>C7_GEN2_CH3_ART2_2</t>
+  </si>
+  <si>
+    <t>C7_GEN2_CH3_ART3</t>
+  </si>
+  <si>
+    <t>C7_GEN2_CH4_ART1</t>
+  </si>
+  <si>
+    <t>C7_GEN2_CH5_ARTXX1</t>
+  </si>
+  <si>
+    <t>C7_GEN2_CH6_ARTX</t>
+  </si>
+  <si>
+    <t>C7-GEN-CH01-ART01</t>
+  </si>
+  <si>
+    <t>C7-GEN-CH01-ART01.1</t>
+  </si>
+  <si>
+    <t>C7_IND04-19_ART5</t>
+  </si>
+  <si>
+    <t>C7-GEN-CH04-ART01.1</t>
+  </si>
+  <si>
+    <t>Dos incisos de sobra</t>
+  </si>
+  <si>
+    <t>C7-GEN-CH07-ART15</t>
+  </si>
+  <si>
+    <t>Una palabra</t>
+  </si>
+  <si>
+    <t>C7-GEN-CH08-ART01</t>
+  </si>
+  <si>
+    <t>C7-GEN-CH08-ART01.1</t>
+  </si>
+  <si>
+    <t>C7_IND04-19_ARTN11</t>
+  </si>
+  <si>
+    <t>C7_IND04-19_ARTN3</t>
+  </si>
+  <si>
+    <t>C7_IND03-19_CH11_ART3</t>
+  </si>
+  <si>
+    <t>C7_IND03-19_CH12_ART1</t>
+  </si>
+  <si>
+    <t>C7_IND03-19_CH13_ART6</t>
+  </si>
+  <si>
+    <t>C7_GEN3_ART1</t>
+  </si>
+  <si>
+    <t>C7_GEN3_ART2</t>
+  </si>
+  <si>
+    <t>C7_GEN3_ART6</t>
+  </si>
+  <si>
+    <t>C7_GEN3_ART11</t>
+  </si>
+  <si>
+    <t>C7_IND04-09-2_ARTN</t>
+  </si>
+  <si>
+    <t>C7_GEN3_ART48</t>
+  </si>
+  <si>
+    <t>C7_GEN3_ART50</t>
+  </si>
+  <si>
+    <t>C7_GEN3_ART53</t>
   </si>
 </sst>
 </file>
@@ -6127,9 +6257,648 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C625EF6D-2FED-45E6-AF0C-2B30004BDDFE}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>458</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>459</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>460</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>462</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>464</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>467</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>468</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>469</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>470</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>471</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>472</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>474</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>477</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>480</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>483</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>484</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>485</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>486</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>489</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>490</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>491</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>492</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>493</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>496</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>498</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>4</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>461</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E27" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>463</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E28" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>465</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>466</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>473</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
+        <v>2</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="E31" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>475</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>2</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="E32" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>476</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>478</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34" t="s">
+        <v>2</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E34" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>479</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35" t="s">
+        <v>2</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E35" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>481</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
+        <v>2</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="E36" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>482</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
+        <v>2</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E37" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>487</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>2</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="E38" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>488</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39" t="s">
+        <v>2</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="E39" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>494</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s">
+        <v>2</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>495</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41" t="s">
+        <v>2</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="E41" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>497</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42" t="s">
+        <v>2</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E42" t="s">
+        <v>353</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G1" xr:uid="{C625EF6D-2FED-45E6-AF0C-2B30004BDDFE}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G42">
+      <sortCondition ref="C1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/coincidencias_comisiones.xlsx
+++ b/coincidencias_comisiones.xlsx
@@ -8,22 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vicel\Proyectos\constitutional-proposal-tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274682E4-40F4-4BC3-B332-8A1DC514EBA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E811FBC0-36C5-4AD8-AD87-95C95CE040EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" activeTab="4" xr2:uid="{EB1ABC4A-685D-416C-81A4-F83CAA4FCE57}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" activeTab="1" xr2:uid="{EB1ABC4A-685D-416C-81A4-F83CAA4FCE57}"/>
   </bookViews>
   <sheets>
     <sheet name="Comisión 1" sheetId="1" r:id="rId1"/>
     <sheet name="Comisión 3" sheetId="2" r:id="rId2"/>
-    <sheet name="Comisión 6" sheetId="3" r:id="rId3"/>
-    <sheet name="Comisión 5" sheetId="4" r:id="rId4"/>
+    <sheet name="Comisión 5" sheetId="4" r:id="rId3"/>
+    <sheet name="Comisión 6" sheetId="3" r:id="rId4"/>
     <sheet name="Comisión 7" sheetId="5" r:id="rId5"/>
+    <sheet name="Total" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comisión 1'!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Comisión 3'!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Comisión 6'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Comisión 5'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Comisión 6'!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Comisión 7'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Total!$A$1:$C$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1686" uniqueCount="427">
   <si>
     <t>Número previo</t>
   </si>
@@ -396,12 +399,6 @@
     <t>C1-GEN-CH03-ART39</t>
   </si>
   <si>
-    <t>C1-IND03-17-CH04-ART42</t>
-  </si>
-  <si>
-    <t>C1-GEN-CH04-ART42</t>
-  </si>
-  <si>
     <t>C1-GEN-CH04-ART43</t>
   </si>
   <si>
@@ -1210,13 +1207,136 @@
   </si>
   <si>
     <t>C7_GEN3_ART53</t>
+  </si>
+  <si>
+    <t>C5-GEN-CH01-ART01</t>
+  </si>
+  <si>
+    <t>C5-IND04-09-2-CH01-ART12A</t>
+  </si>
+  <si>
+    <t>C5-IND04-09-2-CH01-ART12B</t>
+  </si>
+  <si>
+    <t>C5-IND04-09-2-CH01-ART12C</t>
+  </si>
+  <si>
+    <t>C5-IND04-09-2-CH01-ART12D</t>
+  </si>
+  <si>
+    <t>C5-GEN-CH15-ART42</t>
+  </si>
+  <si>
+    <t>C5-GEN-CH18-ART47</t>
+  </si>
+  <si>
+    <t>C5-GEN-CH34-ART73</t>
+  </si>
+  <si>
+    <t>C5-GEN-CH54-ART93</t>
+  </si>
+  <si>
+    <t>C5-GEN2-CH1-ART2</t>
+  </si>
+  <si>
+    <t>C5-GEN2-CH1-ART3</t>
+  </si>
+  <si>
+    <t>C5-GEN2-CH1-ART4</t>
+  </si>
+  <si>
+    <t>C5-GEN2-CH1-ART49</t>
+  </si>
+  <si>
+    <t>C5-GEN2-CH1-ART50</t>
+  </si>
+  <si>
+    <t>C5-GEN2-CH1-ART97</t>
+  </si>
+  <si>
+    <t>C5-GEN2-CH1-ART198</t>
+  </si>
+  <si>
+    <t>C5-GEN2-CH1-ART199</t>
+  </si>
+  <si>
+    <t>C5-IND05-04-CH1-ART27-30</t>
+  </si>
+  <si>
+    <t>C5-GEN2-CH1-ART238</t>
+  </si>
+  <si>
+    <t>C5-GEN2-CH1-ART247</t>
+  </si>
+  <si>
+    <t>C5-GEN2-CH1-ART343</t>
+  </si>
+  <si>
+    <t>C5-GEN2-CH1-ART344</t>
+  </si>
+  <si>
+    <t>C5-GEN2-CH1-ART345</t>
+  </si>
+  <si>
+    <t>C5-GEN2-CH1-ART347</t>
+  </si>
+  <si>
+    <t>C5-GEN-CH22-ART60</t>
+  </si>
+  <si>
+    <t>C5-GEN2-CH1-ART6</t>
+  </si>
+  <si>
+    <t>C5-IND05-04-CH1-ARTNUEVO</t>
+  </si>
+  <si>
+    <t>C5-IND04-09-CH1-ARTN1</t>
+  </si>
+  <si>
+    <t>C5-GEN2-CH1-ART152</t>
+  </si>
+  <si>
+    <t>C5-GEN2-CH1-ART186</t>
+  </si>
+  <si>
+    <t>C5-GEN2-CH1-ART200</t>
+  </si>
+  <si>
+    <t>C5-GEN2-CH1-ART201</t>
+  </si>
+  <si>
+    <t>C5-GEN-CH07-ART21</t>
+  </si>
+  <si>
+    <t>C5-GEN-CH10-ART25</t>
+  </si>
+  <si>
+    <t>C5-GEN2-CH1-ART1</t>
+  </si>
+  <si>
+    <t>C5-GEN2-CH1-ART160</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>C1-IND03-17-CH04-ART42 y C1-GEN-CH04-ART42</t>
+  </si>
+  <si>
+    <t>C6_IND04-27_ART2</t>
+  </si>
+  <si>
+    <t>n</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1242,6 +1362,13 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1260,10 +1387,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1271,11 +1399,34 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1605,7 +1756,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F75798E8-940C-4AF2-9A2E-61B0FF834F11}">
-  <dimension ref="A1:M101"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -1698,7 +1849,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -1729,7 +1880,7 @@
         <v>59</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G8" t="s">
         <v>2</v>
@@ -1746,7 +1897,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -1945,7 +2096,7 @@
         <v>33</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>116</v>
+        <v>424</v>
       </c>
       <c r="G20" t="s">
         <v>2</v>
@@ -1965,7 +2116,7 @@
         <v>32</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G21" t="s">
         <v>2</v>
@@ -1985,7 +2136,7 @@
         <v>31</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G22" t="s">
         <v>2</v>
@@ -2005,7 +2156,7 @@
         <v>30</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G23" t="s">
         <v>2</v>
@@ -2025,7 +2176,7 @@
         <v>29</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G24" t="s">
         <v>2</v>
@@ -2045,7 +2196,7 @@
         <v>27</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G25" t="s">
         <v>2</v>
@@ -2065,7 +2216,7 @@
         <v>20</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G26" t="s">
         <v>2</v>
@@ -2085,7 +2236,7 @@
         <v>19</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G27" t="s">
         <v>2</v>
@@ -2105,7 +2256,7 @@
         <v>18</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G28" t="s">
         <v>2</v>
@@ -2125,7 +2276,7 @@
         <v>16</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G29" t="s">
         <v>2</v>
@@ -2145,7 +2296,7 @@
         <v>15</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G30" t="s">
         <v>2</v>
@@ -2179,7 +2330,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>68</v>
       </c>
@@ -2193,13 +2344,13 @@
         <v>9</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G33" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>69</v>
       </c>
@@ -2213,13 +2364,13 @@
         <v>8</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G34" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>71</v>
       </c>
@@ -2233,7 +2384,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>72</v>
       </c>
@@ -2247,7 +2398,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>75</v>
       </c>
@@ -2261,7 +2412,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>76</v>
       </c>
@@ -2275,7 +2426,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>77</v>
       </c>
@@ -2289,7 +2440,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>78</v>
       </c>
@@ -2303,7 +2454,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>79</v>
       </c>
@@ -2317,7 +2468,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>80</v>
       </c>
@@ -2331,7 +2482,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>82</v>
       </c>
@@ -2345,7 +2496,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>83</v>
       </c>
@@ -2358,12 +2509,8 @@
       <c r="D44" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="M44">
-        <f>96-54</f>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>84</v>
       </c>
@@ -2377,7 +2524,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>87</v>
       </c>
@@ -2391,7 +2538,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>88</v>
       </c>
@@ -2404,11 +2551,9 @@
       <c r="D47" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H47" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="H47" s="1"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>90</v>
       </c>
@@ -2422,7 +2567,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>92</v>
       </c>
@@ -2436,7 +2581,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>95</v>
       </c>
@@ -2450,7 +2595,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>97</v>
       </c>
@@ -2464,7 +2609,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>98</v>
       </c>
@@ -2478,7 +2623,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>99</v>
       </c>
@@ -2492,7 +2637,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>100</v>
       </c>
@@ -2506,82 +2651,49 @@
         <v>64</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55">
+        <v>10</v>
+      </c>
+      <c r="C55" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>23</v>
+      </c>
+      <c r="C56" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>36</v>
+      </c>
+      <c r="C57" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>38</v>
+      </c>
+      <c r="C58" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>53</v>
+      </c>
+      <c r="C59" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A60">
         <v>3</v>
-      </c>
-      <c r="B55">
-        <v>1</v>
-      </c>
-      <c r="C55" t="s">
-        <v>6</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A56">
-        <v>5</v>
-      </c>
-      <c r="B56">
-        <v>1</v>
-      </c>
-      <c r="C56" t="s">
-        <v>6</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A57">
-        <v>8</v>
-      </c>
-      <c r="B57">
-        <v>1</v>
-      </c>
-      <c r="C57" t="s">
-        <v>6</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A58">
-        <v>9</v>
-      </c>
-      <c r="B58">
-        <v>1</v>
-      </c>
-      <c r="C58" t="s">
-        <v>6</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A59">
-        <v>13</v>
-      </c>
-      <c r="B59">
-        <v>1</v>
-      </c>
-      <c r="C59" t="s">
-        <v>6</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A60">
-        <v>15</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -2590,12 +2702,12 @@
         <v>6</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B61">
         <v>1</v>
@@ -2604,12 +2716,12 @@
         <v>6</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B62">
         <v>1</v>
@@ -2618,18 +2730,15 @@
         <v>6</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G62" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B63">
         <v>1</v>
@@ -2638,18 +2747,12 @@
         <v>6</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G63" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B64">
         <v>1</v>
@@ -2658,12 +2761,12 @@
         <v>6</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>54</v>
+        <v>135</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B65">
         <v>1</v>
@@ -2672,12 +2775,12 @@
         <v>6</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B66">
         <v>1</v>
@@ -2686,18 +2789,12 @@
         <v>6</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G66" t="s">
-        <v>2</v>
+        <v>137</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B67">
         <v>1</v>
@@ -2706,12 +2803,18 @@
         <v>6</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G67" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B68">
         <v>1</v>
@@ -2720,10 +2823,10 @@
         <v>6</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G68" t="s">
         <v>2</v>
@@ -2731,7 +2834,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B69">
         <v>1</v>
@@ -2740,12 +2843,12 @@
         <v>6</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B70">
         <v>1</v>
@@ -2754,18 +2857,12 @@
         <v>6</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G70" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B71">
         <v>1</v>
@@ -2774,12 +2871,18 @@
         <v>6</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>10</v>
+        <v>50</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G71" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B72">
         <v>1</v>
@@ -2788,18 +2891,12 @@
         <v>6</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="G72" t="s">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -2808,10 +2905,10 @@
         <v>6</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G73" t="s">
         <v>2</v>
@@ -2819,7 +2916,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B74">
         <v>1</v>
@@ -2828,12 +2925,12 @@
         <v>6</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B75">
         <v>1</v>
@@ -2842,12 +2939,18 @@
         <v>6</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="G75" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B76">
         <v>1</v>
@@ -2856,18 +2959,12 @@
         <v>6</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G76" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B77">
         <v>1</v>
@@ -2876,10 +2973,10 @@
         <v>6</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G77" t="s">
         <v>2</v>
@@ -2887,7 +2984,7 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="B78">
         <v>1</v>
@@ -2896,10 +2993,10 @@
         <v>6</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="G78" t="s">
         <v>2</v>
@@ -2907,7 +3004,7 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="B79">
         <v>1</v>
@@ -2916,18 +3013,12 @@
         <v>6</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="G79" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B80">
         <v>1</v>
@@ -2936,12 +3027,12 @@
         <v>6</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B81">
         <v>1</v>
@@ -2950,10 +3041,10 @@
         <v>6</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="G81" t="s">
         <v>2</v>
@@ -2961,7 +3052,7 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B82">
         <v>1</v>
@@ -2970,12 +3061,18 @@
         <v>6</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G82" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B83">
         <v>1</v>
@@ -2984,10 +3081,10 @@
         <v>6</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="G83" t="s">
         <v>2</v>
@@ -2995,7 +3092,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B84">
         <v>1</v>
@@ -3004,10 +3101,10 @@
         <v>6</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G84" t="s">
         <v>2</v>
@@ -3015,7 +3112,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B85">
         <v>1</v>
@@ -3024,18 +3121,12 @@
         <v>6</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="G85" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="B86">
         <v>1</v>
@@ -3044,12 +3135,18 @@
         <v>6</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>7</v>
+        <v>24</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G86" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="B87">
         <v>1</v>
@@ -3058,12 +3155,12 @@
         <v>6</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>90</v>
+        <v>23</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="B88">
         <v>1</v>
@@ -3072,12 +3169,18 @@
         <v>6</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>141</v>
+        <v>22</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="G88" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="B89">
         <v>1</v>
@@ -3086,12 +3189,18 @@
         <v>6</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>83</v>
+        <v>21</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G89" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="B90">
         <v>1</v>
@@ -3100,12 +3209,18 @@
         <v>6</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>79</v>
+        <v>13</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="G90" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="B91">
         <v>1</v>
@@ -3114,12 +3229,12 @@
         <v>6</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>78</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="B92">
         <v>1</v>
@@ -3128,12 +3243,12 @@
         <v>6</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="B93">
         <v>1</v>
@@ -3142,12 +3257,12 @@
         <v>6</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>73</v>
+        <v>139</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="B94">
         <v>1</v>
@@ -3156,12 +3271,12 @@
         <v>6</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="B95">
         <v>1</v>
@@ -3170,12 +3285,12 @@
         <v>6</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B96">
         <v>1</v>
@@ -3184,32 +3299,77 @@
         <v>6</v>
       </c>
       <c r="D96" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <v>89</v>
+      </c>
+      <c r="B97">
+        <v>1</v>
+      </c>
+      <c r="C97" t="s">
+        <v>6</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <v>91</v>
+      </c>
+      <c r="B98">
+        <v>1</v>
+      </c>
+      <c r="C98" t="s">
+        <v>6</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>93</v>
+      </c>
+      <c r="B99">
+        <v>1</v>
+      </c>
+      <c r="C99" t="s">
+        <v>6</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <v>94</v>
+      </c>
+      <c r="B100">
+        <v>1</v>
+      </c>
+      <c r="C100" t="s">
+        <v>6</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>96</v>
+      </c>
+      <c r="B101">
+        <v>1</v>
+      </c>
+      <c r="C101" t="s">
+        <v>6</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>68</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A97">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A98">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A99">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A100">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A101">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -3262,7 +3422,7 @@
         <v>4</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -3276,7 +3436,7 @@
         <v>4</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -3290,7 +3450,7 @@
         <v>4</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -3304,7 +3464,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -3318,7 +3478,7 @@
         <v>4</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F6" s="1"/>
     </row>
@@ -3333,7 +3493,7 @@
         <v>4</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -3347,7 +3507,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
@@ -3361,7 +3521,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F9" s="1"/>
     </row>
@@ -3376,7 +3536,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F10" s="1"/>
     </row>
@@ -3391,7 +3551,7 @@
         <v>4</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F11" s="1"/>
     </row>
@@ -3406,7 +3566,7 @@
         <v>4</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F12" s="1"/>
     </row>
@@ -3421,7 +3581,7 @@
         <v>4</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F13" s="1"/>
     </row>
@@ -3436,7 +3596,7 @@
         <v>4</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
@@ -3450,7 +3610,7 @@
         <v>4</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F15" s="1"/>
     </row>
@@ -3465,7 +3625,7 @@
         <v>4</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F16" s="1"/>
     </row>
@@ -3480,7 +3640,7 @@
         <v>4</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F17" s="1"/>
     </row>
@@ -3495,7 +3655,7 @@
         <v>4</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F18" s="1"/>
     </row>
@@ -3510,7 +3670,7 @@
         <v>4</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -3524,7 +3684,7 @@
         <v>4</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -3538,7 +3698,7 @@
         <v>4</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -3552,7 +3712,7 @@
         <v>4</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -3566,7 +3726,7 @@
         <v>4</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F23" s="1"/>
     </row>
@@ -3581,7 +3741,7 @@
         <v>4</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F24" s="1"/>
     </row>
@@ -3596,7 +3756,7 @@
         <v>4</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F25" s="1"/>
     </row>
@@ -3611,7 +3771,7 @@
         <v>4</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
@@ -3625,7 +3785,7 @@
         <v>4</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F27" s="1"/>
     </row>
@@ -3640,7 +3800,7 @@
         <v>4</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
@@ -3654,7 +3814,7 @@
         <v>4</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F29" s="1"/>
     </row>
@@ -3669,7 +3829,7 @@
         <v>4</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F30" s="1"/>
     </row>
@@ -3684,7 +3844,7 @@
         <v>4</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
@@ -3698,7 +3858,7 @@
         <v>4</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
@@ -3712,7 +3872,7 @@
         <v>4</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F33" s="1"/>
     </row>
@@ -3727,7 +3887,7 @@
         <v>4</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F34" s="1"/>
     </row>
@@ -3742,7 +3902,7 @@
         <v>4</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F35" s="1"/>
     </row>
@@ -3757,7 +3917,7 @@
         <v>4</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -3771,7 +3931,7 @@
         <v>4</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F37" s="1"/>
     </row>
@@ -3786,7 +3946,7 @@
         <v>4</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F38" s="1"/>
     </row>
@@ -3801,7 +3961,7 @@
         <v>4</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F39" s="1"/>
     </row>
@@ -3816,7 +3976,7 @@
         <v>4</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F40" s="1"/>
     </row>
@@ -3831,7 +3991,7 @@
         <v>4</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
@@ -3845,7 +4005,7 @@
         <v>4</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
@@ -3859,7 +4019,7 @@
         <v>4</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
@@ -3873,7 +4033,7 @@
         <v>4</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
@@ -3887,7 +4047,7 @@
         <v>4</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
@@ -3901,7 +4061,7 @@
         <v>4</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
@@ -3915,7 +4075,7 @@
         <v>4</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
@@ -3929,7 +4089,7 @@
         <v>4</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
@@ -3943,7 +4103,7 @@
         <v>2</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
@@ -3957,10 +4117,10 @@
         <v>2</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E50" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
@@ -3974,10 +4134,10 @@
         <v>2</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E51" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F51" s="1"/>
     </row>
@@ -3992,10 +4152,10 @@
         <v>2</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E52" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
@@ -4009,7 +4169,7 @@
         <v>2</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F53" s="1"/>
     </row>
@@ -4024,10 +4184,10 @@
         <v>2</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E54" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F54" s="1"/>
     </row>
@@ -4042,10 +4202,10 @@
         <v>2</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E55" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F55" s="1"/>
     </row>
@@ -4060,7 +4220,7 @@
         <v>2</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F56" s="1"/>
     </row>
@@ -4075,10 +4235,10 @@
         <v>2</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E57" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F57" s="1"/>
     </row>
@@ -4093,10 +4253,10 @@
         <v>2</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E58" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F58" s="1"/>
     </row>
@@ -4111,10 +4271,10 @@
         <v>2</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E59" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F59" s="1"/>
     </row>
@@ -4129,10 +4289,10 @@
         <v>2</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E60" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F60" s="1"/>
     </row>
@@ -4147,10 +4307,10 @@
         <v>2</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E61" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
@@ -4164,10 +4324,10 @@
         <v>2</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E62" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
@@ -4181,7 +4341,7 @@
         <v>2</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
@@ -4195,10 +4355,10 @@
         <v>2</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E64" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
@@ -4212,10 +4372,10 @@
         <v>2</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E65" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
@@ -4229,10 +4389,10 @@
         <v>2</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E66" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F66" s="1"/>
     </row>
@@ -4247,7 +4407,7 @@
         <v>2</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F67" s="1"/>
     </row>
@@ -4262,10 +4422,10 @@
         <v>2</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E68" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
@@ -4279,10 +4439,10 @@
         <v>2</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E69" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4296,7 +4456,7 @@
         <v>2</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
@@ -4310,10 +4470,10 @@
         <v>2</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E71" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
@@ -4327,16 +4487,19 @@
         <v>2</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E72" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>173</v>
       </c>
+      <c r="C73" t="s">
+        <v>422</v>
+      </c>
       <c r="D73" s="1"/>
       <c r="F73" s="1"/>
     </row>
@@ -4344,6 +4507,9 @@
       <c r="A74">
         <v>174</v>
       </c>
+      <c r="C74" t="s">
+        <v>422</v>
+      </c>
       <c r="D74" s="1"/>
       <c r="F74" s="1"/>
     </row>
@@ -4351,137 +4517,206 @@
       <c r="A75">
         <v>175</v>
       </c>
+      <c r="C75" t="s">
+        <v>422</v>
+      </c>
       <c r="D75" s="1"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>176</v>
       </c>
+      <c r="C76" t="s">
+        <v>422</v>
+      </c>
       <c r="D76" s="1"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>177</v>
       </c>
+      <c r="C77" t="s">
+        <v>422</v>
+      </c>
       <c r="D77" s="1"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>178</v>
       </c>
+      <c r="C78" t="s">
+        <v>422</v>
+      </c>
       <c r="D78" s="1"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>179</v>
       </c>
+      <c r="C79" t="s">
+        <v>422</v>
+      </c>
       <c r="D79" s="1"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>180</v>
       </c>
+      <c r="C80" t="s">
+        <v>422</v>
+      </c>
       <c r="D80" s="1"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>181</v>
       </c>
+      <c r="C81" t="s">
+        <v>422</v>
+      </c>
       <c r="D81" s="1"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>182</v>
       </c>
+      <c r="C82" t="s">
+        <v>422</v>
+      </c>
       <c r="D82" s="1"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>183</v>
       </c>
+      <c r="C83" t="s">
+        <v>422</v>
+      </c>
       <c r="D83" s="1"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>184</v>
       </c>
+      <c r="C84" t="s">
+        <v>422</v>
+      </c>
       <c r="D84" s="1"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>185</v>
       </c>
+      <c r="C85" t="s">
+        <v>422</v>
+      </c>
       <c r="D85" s="1"/>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>186</v>
       </c>
+      <c r="C86" t="s">
+        <v>422</v>
+      </c>
       <c r="D86" s="1"/>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>187</v>
       </c>
+      <c r="C87" t="s">
+        <v>422</v>
+      </c>
       <c r="D87" s="1"/>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>188</v>
       </c>
+      <c r="C88" t="s">
+        <v>422</v>
+      </c>
       <c r="D88" s="1"/>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>189</v>
       </c>
+      <c r="C89" t="s">
+        <v>422</v>
+      </c>
       <c r="D89" s="1"/>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>190</v>
       </c>
+      <c r="C90" t="s">
+        <v>422</v>
+      </c>
       <c r="D90" s="1"/>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>191</v>
       </c>
+      <c r="C91" t="s">
+        <v>422</v>
+      </c>
       <c r="D91" s="1"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>192</v>
       </c>
+      <c r="C92" t="s">
+        <v>422</v>
+      </c>
       <c r="D92" s="1"/>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>193</v>
       </c>
+      <c r="C93" t="s">
+        <v>422</v>
+      </c>
       <c r="D93" s="1"/>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>194</v>
       </c>
+      <c r="C94" t="s">
+        <v>422</v>
+      </c>
       <c r="D94" s="1"/>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>195</v>
       </c>
+      <c r="C95" t="s">
+        <v>422</v>
+      </c>
       <c r="D95" s="1"/>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>196</v>
       </c>
+      <c r="C96" t="s">
+        <v>422</v>
+      </c>
       <c r="D96" s="1"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>197</v>
+      </c>
+      <c r="C97" t="s">
+        <v>422</v>
       </c>
       <c r="D97" s="1"/>
       <c r="E97" s="1"/>
@@ -4498,6 +4733,611 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF016F2B-E88B-426D-8061-4E20A3875DD7}">
+  <dimension ref="A1:G44"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>296</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>297</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>298</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>299</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>300</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>301</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>302</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>303</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>304</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>305</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>306</v>
+      </c>
+      <c r="C12" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>307</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>308</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>309</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>310</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>311</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>312</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>313</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>314</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>315</v>
+      </c>
+      <c r="C21" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>316</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>317</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>318</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>319</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>320</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>321</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>322</v>
+      </c>
+      <c r="C28" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>323</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>324</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
+        <v>4</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>325</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>326</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>2</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>327</v>
+      </c>
+      <c r="C33" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>328</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34" t="s">
+        <v>2</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>329</v>
+      </c>
+      <c r="C35" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>330</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
+        <v>2</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>331</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>332</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>333</v>
+      </c>
+      <c r="C39" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>334</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s">
+        <v>4</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>335</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41" t="s">
+        <v>4</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>336</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42" t="s">
+        <v>4</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>337</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s">
+        <v>4</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>338</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44" t="s">
+        <v>2</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G1" xr:uid="{EF016F2B-E88B-426D-8061-4E20A3875DD7}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G44">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5520BB1-FD64-4562-8A4D-B7ECF35F2484}">
   <dimension ref="A1:G120"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4536,7 +5376,7 @@
         <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -4550,7 +5390,7 @@
         <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -4564,7 +5404,7 @@
         <v>4</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -4578,7 +5418,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -4592,7 +5432,7 @@
         <v>4</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -4606,7 +5446,7 @@
         <v>4</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -4620,7 +5460,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
@@ -4634,7 +5474,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -4648,7 +5488,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -4662,7 +5502,7 @@
         <v>4</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
@@ -4676,7 +5516,7 @@
         <v>4</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -4690,7 +5530,7 @@
         <v>4</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
@@ -4704,7 +5544,7 @@
         <v>4</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
@@ -4718,7 +5558,7 @@
         <v>4</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
@@ -4732,7 +5572,7 @@
         <v>4</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -4746,7 +5586,7 @@
         <v>4</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -4760,7 +5600,7 @@
         <v>4</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -4774,7 +5614,7 @@
         <v>4</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -4788,7 +5628,7 @@
         <v>4</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -4802,7 +5642,7 @@
         <v>4</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -4816,7 +5656,7 @@
         <v>4</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -4830,7 +5670,7 @@
         <v>4</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -4844,7 +5684,7 @@
         <v>4</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -4858,7 +5698,7 @@
         <v>4</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -4872,7 +5712,7 @@
         <v>4</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -4886,7 +5726,7 @@
         <v>4</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
@@ -4900,7 +5740,7 @@
         <v>4</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -4914,7 +5754,7 @@
         <v>4</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
@@ -4928,7 +5768,7 @@
         <v>4</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
@@ -4942,7 +5782,7 @@
         <v>4</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
@@ -4956,7 +5796,7 @@
         <v>4</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
@@ -4970,7 +5810,7 @@
         <v>4</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
@@ -4984,7 +5824,7 @@
         <v>4</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
@@ -4998,7 +5838,7 @@
         <v>4</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
@@ -5012,7 +5852,7 @@
         <v>4</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
@@ -5026,7 +5866,7 @@
         <v>4</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
@@ -5040,7 +5880,7 @@
         <v>4</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
@@ -5054,7 +5894,7 @@
         <v>4</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
@@ -5068,7 +5908,7 @@
         <v>4</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
@@ -5082,7 +5922,7 @@
         <v>4</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>269</v>
+        <v>425</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
@@ -5096,7 +5936,7 @@
         <v>4</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
@@ -5110,7 +5950,7 @@
         <v>4</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
@@ -5124,7 +5964,7 @@
         <v>4</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
@@ -5138,7 +5978,7 @@
         <v>4</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
@@ -5152,7 +5992,7 @@
         <v>4</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
@@ -5166,7 +6006,7 @@
         <v>4</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
@@ -5180,7 +6020,7 @@
         <v>4</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
@@ -5194,7 +6034,7 @@
         <v>4</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
@@ -5208,7 +6048,7 @@
         <v>4</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
@@ -5222,7 +6062,7 @@
         <v>4</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
@@ -5236,7 +6076,7 @@
         <v>4</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
@@ -5250,7 +6090,7 @@
         <v>4</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
@@ -5264,7 +6104,7 @@
         <v>4</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
@@ -5278,7 +6118,7 @@
         <v>4</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
@@ -5292,7 +6132,7 @@
         <v>4</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
@@ -5306,7 +6146,7 @@
         <v>4</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
@@ -5320,7 +6160,7 @@
         <v>4</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
@@ -5334,7 +6174,7 @@
         <v>4</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
@@ -5348,7 +6188,7 @@
         <v>4</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
@@ -5362,7 +6202,7 @@
         <v>4</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
@@ -5376,7 +6216,7 @@
         <v>4</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
@@ -5390,7 +6230,7 @@
         <v>4</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
@@ -5404,7 +6244,7 @@
         <v>4</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
@@ -5418,7 +6258,7 @@
         <v>4</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
@@ -5432,7 +6272,7 @@
         <v>4</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
@@ -5446,7 +6286,7 @@
         <v>4</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
@@ -5460,7 +6300,7 @@
         <v>4</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
@@ -5474,7 +6314,7 @@
         <v>4</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
@@ -5488,7 +6328,7 @@
         <v>4</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
@@ -5502,7 +6342,7 @@
         <v>4</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
@@ -5516,7 +6356,7 @@
         <v>4</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
@@ -5530,7 +6370,7 @@
         <v>4</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
@@ -5544,7 +6384,7 @@
         <v>4</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
@@ -5558,7 +6398,7 @@
         <v>4</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
@@ -5572,7 +6412,7 @@
         <v>4</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
@@ -5586,7 +6426,7 @@
         <v>4</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
@@ -5600,7 +6440,7 @@
         <v>4</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
@@ -5614,7 +6454,7 @@
         <v>4</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
@@ -5628,7 +6468,7 @@
         <v>4</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
@@ -5642,7 +6482,7 @@
         <v>4</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
@@ -5656,7 +6496,7 @@
         <v>4</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
@@ -5670,7 +6510,7 @@
         <v>4</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
@@ -5684,7 +6524,7 @@
         <v>4</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
@@ -5698,7 +6538,7 @@
         <v>4</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
@@ -5712,7 +6552,7 @@
         <v>4</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
@@ -5726,7 +6566,7 @@
         <v>4</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
@@ -5740,7 +6580,7 @@
         <v>4</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
@@ -5754,7 +6594,7 @@
         <v>4</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
@@ -5768,7 +6608,7 @@
         <v>4</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
@@ -5782,7 +6622,7 @@
         <v>4</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
@@ -5796,7 +6636,7 @@
         <v>4</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
@@ -5810,7 +6650,7 @@
         <v>4</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
@@ -5824,7 +6664,7 @@
         <v>4</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
@@ -5838,7 +6678,7 @@
         <v>4</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
@@ -5852,7 +6692,7 @@
         <v>4</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.35">
@@ -5866,7 +6706,7 @@
         <v>4</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.35">
@@ -5880,10 +6720,10 @@
         <v>4</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E98" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.35">
@@ -5897,7 +6737,7 @@
         <v>4</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.35">
@@ -5911,7 +6751,7 @@
         <v>4</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.35">
@@ -5925,7 +6765,7 @@
         <v>4</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.35">
@@ -5939,7 +6779,7 @@
         <v>2</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.35">
@@ -5953,10 +6793,10 @@
         <v>2</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E103" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.35">
@@ -5970,10 +6810,10 @@
         <v>2</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E104" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.35">
@@ -5987,10 +6827,10 @@
         <v>2</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E105" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.35">
@@ -6004,7 +6844,7 @@
         <v>2</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.35">
@@ -6018,10 +6858,10 @@
         <v>2</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E107" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.35">
@@ -6035,10 +6875,10 @@
         <v>2</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E108" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.35">
@@ -6052,10 +6892,10 @@
         <v>2</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E109" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.35">
@@ -6069,10 +6909,10 @@
         <v>2</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E110" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.35">
@@ -6086,10 +6926,10 @@
         <v>2</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E111" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.35">
@@ -6103,10 +6943,10 @@
         <v>2</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E112" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.35">
@@ -6120,10 +6960,10 @@
         <v>2</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E113" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.35">
@@ -6137,10 +6977,10 @@
         <v>2</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E114" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.35">
@@ -6154,10 +6994,10 @@
         <v>2</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E115" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.35">
@@ -6171,10 +7011,10 @@
         <v>2</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E116" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.35">
@@ -6188,10 +7028,10 @@
         <v>2</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E117" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.35">
@@ -6205,7 +7045,7 @@
         <v>2</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.35">
@@ -6219,7 +7059,7 @@
         <v>2</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.35">
@@ -6227,13 +7067,16 @@
         <v>350</v>
       </c>
       <c r="B120">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="C120" t="s">
+        <v>2</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E120" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -6242,15 +7085,9 @@
       <sortCondition ref="C1"/>
     </sortState>
   </autoFilter>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF016F2B-E88B-426D-8061-4E20A3875DD7}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <conditionalFormatting sqref="D2:D40 D42:D120">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6294,7 +7131,7 @@
         <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -6308,7 +7145,7 @@
         <v>4</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -6322,7 +7159,7 @@
         <v>4</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -6336,7 +7173,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -6350,7 +7187,7 @@
         <v>4</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -6364,7 +7201,7 @@
         <v>4</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -6378,7 +7215,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
@@ -6392,7 +7229,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -6406,7 +7243,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -6420,7 +7257,7 @@
         <v>4</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
@@ -6434,7 +7271,7 @@
         <v>4</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -6448,7 +7285,7 @@
         <v>4</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
@@ -6462,7 +7299,7 @@
         <v>4</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
@@ -6476,7 +7313,7 @@
         <v>4</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
@@ -6490,7 +7327,7 @@
         <v>4</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -6504,7 +7341,7 @@
         <v>4</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -6518,7 +7355,7 @@
         <v>4</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -6532,7 +7369,7 @@
         <v>4</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -6546,7 +7383,7 @@
         <v>4</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
@@ -6560,7 +7397,7 @@
         <v>4</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
@@ -6574,7 +7411,7 @@
         <v>4</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
@@ -6588,7 +7425,7 @@
         <v>4</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -6602,7 +7439,7 @@
         <v>4</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
@@ -6616,7 +7453,7 @@
         <v>4</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
@@ -6630,7 +7467,7 @@
         <v>4</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
@@ -6644,10 +7481,10 @@
         <v>2</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E27" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
@@ -6661,10 +7498,10 @@
         <v>2</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E28" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
@@ -6678,7 +7515,7 @@
         <v>2</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
@@ -6692,7 +7529,7 @@
         <v>2</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
@@ -6706,10 +7543,10 @@
         <v>2</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E31" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
@@ -6723,10 +7560,10 @@
         <v>2</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E32" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
@@ -6740,7 +7577,7 @@
         <v>2</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
@@ -6754,10 +7591,10 @@
         <v>2</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E34" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
@@ -6771,10 +7608,10 @@
         <v>2</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E35" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
@@ -6788,10 +7625,10 @@
         <v>2</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E36" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
@@ -6805,10 +7642,10 @@
         <v>2</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E37" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
@@ -6822,10 +7659,10 @@
         <v>2</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E38" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
@@ -6839,10 +7676,10 @@
         <v>2</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E39" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
@@ -6856,7 +7693,7 @@
         <v>2</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
@@ -6870,10 +7707,10 @@
         <v>2</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E41" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
@@ -6887,10 +7724,10 @@
         <v>2</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E42" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -6901,4 +7738,4382 @@
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7034A0F2-F044-457F-8383-77C15214A3A3}">
+  <dimension ref="A1:K400"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" t="s">
+        <v>426</v>
+      </c>
+      <c r="K1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <f>COUNTIF(B2:B400,"Idéntico")</f>
+        <v>252</v>
+      </c>
+      <c r="K2" s="3">
+        <f>J2/SUM($J$2:$J$4)</f>
+        <v>0.63157894736842102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <f>COUNTIF(B2:B400,"Similar")</f>
+        <v>111</v>
+      </c>
+      <c r="K3" s="3">
+        <f t="shared" ref="K3:K4" si="0">J3/SUM($J$2:$J$4)</f>
+        <v>0.2781954887218045</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" t="s">
+        <v>422</v>
+      </c>
+      <c r="J4">
+        <f>COUNTIF(B3:B401,"NA")</f>
+        <v>36</v>
+      </c>
+      <c r="K4" s="3">
+        <f t="shared" si="0"/>
+        <v>9.0225563909774431E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>5</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>5</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>5</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>5</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>5</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>5</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>5</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>5</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>5</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>5</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>5</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>5</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>5</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>5</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>5</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>5</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>5</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>5</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>5</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>5</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>5</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>5</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>5</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>5</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>5</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>5</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>5</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>5</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>5</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>5</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>5</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>5</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>5</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>5</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>5</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <v>142</v>
+      </c>
+      <c r="B102" t="s">
+        <v>4</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>143</v>
+      </c>
+      <c r="B103" t="s">
+        <v>2</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A104">
+        <v>144</v>
+      </c>
+      <c r="B104" t="s">
+        <v>4</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <v>145</v>
+      </c>
+      <c r="B105" t="s">
+        <v>2</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A106">
+        <v>146</v>
+      </c>
+      <c r="B106" t="s">
+        <v>4</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A107">
+        <v>147</v>
+      </c>
+      <c r="B107" t="s">
+        <v>4</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A108">
+        <v>148</v>
+      </c>
+      <c r="B108" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A109">
+        <v>149</v>
+      </c>
+      <c r="B109" t="s">
+        <v>4</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A110">
+        <v>150</v>
+      </c>
+      <c r="B110" t="s">
+        <v>2</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A111">
+        <v>151</v>
+      </c>
+      <c r="B111" t="s">
+        <v>2</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A112">
+        <v>152</v>
+      </c>
+      <c r="B112" t="s">
+        <v>4</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A113">
+        <v>153</v>
+      </c>
+      <c r="B113" t="s">
+        <v>2</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A114">
+        <v>154</v>
+      </c>
+      <c r="B114" t="s">
+        <v>4</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A115">
+        <v>155</v>
+      </c>
+      <c r="B115" t="s">
+        <v>4</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A116">
+        <v>156</v>
+      </c>
+      <c r="B116" t="s">
+        <v>4</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A117">
+        <v>157</v>
+      </c>
+      <c r="B117" t="s">
+        <v>4</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A118">
+        <v>158</v>
+      </c>
+      <c r="B118" t="s">
+        <v>4</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A119">
+        <v>159</v>
+      </c>
+      <c r="B119" t="s">
+        <v>4</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A120">
+        <v>160</v>
+      </c>
+      <c r="B120" t="s">
+        <v>4</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A121">
+        <v>161</v>
+      </c>
+      <c r="B121" t="s">
+        <v>2</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A122">
+        <v>162</v>
+      </c>
+      <c r="B122" t="s">
+        <v>4</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A123">
+        <v>163</v>
+      </c>
+      <c r="B123" t="s">
+        <v>2</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A124">
+        <v>164</v>
+      </c>
+      <c r="B124" t="s">
+        <v>4</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A125">
+        <v>165</v>
+      </c>
+      <c r="B125" t="s">
+        <v>2</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A126">
+        <v>166</v>
+      </c>
+      <c r="B126" t="s">
+        <v>2</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A127">
+        <v>167</v>
+      </c>
+      <c r="B127" t="s">
+        <v>2</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A128">
+        <v>168</v>
+      </c>
+      <c r="B128" t="s">
+        <v>4</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A129">
+        <v>169</v>
+      </c>
+      <c r="B129" t="s">
+        <v>2</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A130">
+        <v>170</v>
+      </c>
+      <c r="B130" t="s">
+        <v>2</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A131">
+        <v>171</v>
+      </c>
+      <c r="B131" t="s">
+        <v>4</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A132">
+        <v>172</v>
+      </c>
+      <c r="B132" t="s">
+        <v>2</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A133">
+        <v>173</v>
+      </c>
+      <c r="B133" t="s">
+        <v>422</v>
+      </c>
+      <c r="C133" s="1"/>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A134">
+        <v>174</v>
+      </c>
+      <c r="B134" t="s">
+        <v>422</v>
+      </c>
+      <c r="C134" s="1"/>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A135">
+        <v>175</v>
+      </c>
+      <c r="B135" t="s">
+        <v>422</v>
+      </c>
+      <c r="C135" s="1"/>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A136">
+        <v>176</v>
+      </c>
+      <c r="B136" t="s">
+        <v>422</v>
+      </c>
+      <c r="C136" s="1"/>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A137">
+        <v>177</v>
+      </c>
+      <c r="B137" t="s">
+        <v>422</v>
+      </c>
+      <c r="C137" s="1"/>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A138">
+        <v>178</v>
+      </c>
+      <c r="B138" t="s">
+        <v>422</v>
+      </c>
+      <c r="C138" s="1"/>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A139">
+        <v>179</v>
+      </c>
+      <c r="B139" t="s">
+        <v>422</v>
+      </c>
+      <c r="C139" s="1"/>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A140">
+        <v>180</v>
+      </c>
+      <c r="B140" t="s">
+        <v>422</v>
+      </c>
+      <c r="C140" s="1"/>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A141">
+        <v>181</v>
+      </c>
+      <c r="B141" t="s">
+        <v>422</v>
+      </c>
+      <c r="C141" s="1"/>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A142">
+        <v>182</v>
+      </c>
+      <c r="B142" t="s">
+        <v>422</v>
+      </c>
+      <c r="C142" s="1"/>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A143">
+        <v>183</v>
+      </c>
+      <c r="B143" t="s">
+        <v>422</v>
+      </c>
+      <c r="C143" s="1"/>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A144">
+        <v>184</v>
+      </c>
+      <c r="B144" t="s">
+        <v>422</v>
+      </c>
+      <c r="C144" s="1"/>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A145">
+        <v>185</v>
+      </c>
+      <c r="B145" t="s">
+        <v>422</v>
+      </c>
+      <c r="C145" s="1"/>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A146">
+        <v>186</v>
+      </c>
+      <c r="B146" t="s">
+        <v>422</v>
+      </c>
+      <c r="C146" s="1"/>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A147">
+        <v>187</v>
+      </c>
+      <c r="B147" t="s">
+        <v>422</v>
+      </c>
+      <c r="C147" s="1"/>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A148">
+        <v>188</v>
+      </c>
+      <c r="B148" t="s">
+        <v>422</v>
+      </c>
+      <c r="C148" s="1"/>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A149">
+        <v>189</v>
+      </c>
+      <c r="B149" t="s">
+        <v>422</v>
+      </c>
+      <c r="C149" s="1"/>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A150">
+        <v>190</v>
+      </c>
+      <c r="B150" t="s">
+        <v>422</v>
+      </c>
+      <c r="C150" s="1"/>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A151">
+        <v>191</v>
+      </c>
+      <c r="B151" t="s">
+        <v>422</v>
+      </c>
+      <c r="C151" s="1"/>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A152">
+        <v>192</v>
+      </c>
+      <c r="B152" t="s">
+        <v>422</v>
+      </c>
+      <c r="C152" s="1"/>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A153">
+        <v>193</v>
+      </c>
+      <c r="B153" t="s">
+        <v>422</v>
+      </c>
+      <c r="C153" s="1"/>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A154">
+        <v>194</v>
+      </c>
+      <c r="B154" t="s">
+        <v>422</v>
+      </c>
+      <c r="C154" s="1"/>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A155">
+        <v>195</v>
+      </c>
+      <c r="B155" t="s">
+        <v>422</v>
+      </c>
+      <c r="C155" s="1"/>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A156">
+        <v>196</v>
+      </c>
+      <c r="B156" t="s">
+        <v>422</v>
+      </c>
+      <c r="C156" s="1"/>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A157">
+        <v>197</v>
+      </c>
+      <c r="B157" t="s">
+        <v>422</v>
+      </c>
+      <c r="C157" s="1"/>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A158">
+        <v>198</v>
+      </c>
+      <c r="B158" t="s">
+        <v>4</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A159">
+        <v>199</v>
+      </c>
+      <c r="B159" t="s">
+        <v>4</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A160">
+        <v>200</v>
+      </c>
+      <c r="B160" t="s">
+        <v>4</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A161">
+        <v>201</v>
+      </c>
+      <c r="B161" t="s">
+        <v>2</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A162">
+        <v>202</v>
+      </c>
+      <c r="B162" t="s">
+        <v>4</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A163">
+        <v>203</v>
+      </c>
+      <c r="B163" t="s">
+        <v>4</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A164">
+        <v>204</v>
+      </c>
+      <c r="B164" t="s">
+        <v>2</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A165">
+        <v>205</v>
+      </c>
+      <c r="B165" t="s">
+        <v>2</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A166">
+        <v>206</v>
+      </c>
+      <c r="B166" t="s">
+        <v>4</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A167">
+        <v>207</v>
+      </c>
+      <c r="B167" t="s">
+        <v>2</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A168">
+        <v>208</v>
+      </c>
+      <c r="B168" t="s">
+        <v>2</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A169">
+        <v>209</v>
+      </c>
+      <c r="B169" t="s">
+        <v>4</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A170">
+        <v>210</v>
+      </c>
+      <c r="B170" t="s">
+        <v>4</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A171">
+        <v>211</v>
+      </c>
+      <c r="B171" t="s">
+        <v>4</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A172">
+        <v>212</v>
+      </c>
+      <c r="B172" t="s">
+        <v>4</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A173">
+        <v>213</v>
+      </c>
+      <c r="B173" t="s">
+        <v>4</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A174">
+        <v>214</v>
+      </c>
+      <c r="B174" t="s">
+        <v>4</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A175">
+        <v>215</v>
+      </c>
+      <c r="B175" t="s">
+        <v>4</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A176">
+        <v>216</v>
+      </c>
+      <c r="B176" t="s">
+        <v>4</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A177">
+        <v>217</v>
+      </c>
+      <c r="B177" t="s">
+        <v>4</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A178">
+        <v>218</v>
+      </c>
+      <c r="B178" t="s">
+        <v>4</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A179">
+        <v>219</v>
+      </c>
+      <c r="B179" t="s">
+        <v>2</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A180">
+        <v>220</v>
+      </c>
+      <c r="B180" t="s">
+        <v>4</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A181">
+        <v>221</v>
+      </c>
+      <c r="B181" t="s">
+        <v>4</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A182">
+        <v>222</v>
+      </c>
+      <c r="B182" t="s">
+        <v>2</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A183">
+        <v>223</v>
+      </c>
+      <c r="B183" t="s">
+        <v>4</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A184">
+        <v>224</v>
+      </c>
+      <c r="B184" t="s">
+        <v>4</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A185">
+        <v>225</v>
+      </c>
+      <c r="B185" t="s">
+        <v>4</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A186">
+        <v>226</v>
+      </c>
+      <c r="B186" t="s">
+        <v>4</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A187">
+        <v>227</v>
+      </c>
+      <c r="B187" t="s">
+        <v>4</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A188">
+        <v>228</v>
+      </c>
+      <c r="B188" t="s">
+        <v>2</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A189">
+        <v>229</v>
+      </c>
+      <c r="B189" t="s">
+        <v>4</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A190">
+        <v>230</v>
+      </c>
+      <c r="B190" t="s">
+        <v>2</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A191">
+        <v>231</v>
+      </c>
+      <c r="B191" t="s">
+        <v>2</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A192">
+        <v>232</v>
+      </c>
+      <c r="B192" t="s">
+        <v>2</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A193">
+        <v>233</v>
+      </c>
+      <c r="B193" t="s">
+        <v>4</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A194">
+        <v>234</v>
+      </c>
+      <c r="B194" t="s">
+        <v>4</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A195">
+        <v>235</v>
+      </c>
+      <c r="B195" t="s">
+        <v>4</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A196">
+        <v>236</v>
+      </c>
+      <c r="B196" t="s">
+        <v>4</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A197">
+        <v>237</v>
+      </c>
+      <c r="B197" t="s">
+        <v>4</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A198">
+        <v>296</v>
+      </c>
+      <c r="B198" t="s">
+        <v>4</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A199">
+        <v>297</v>
+      </c>
+      <c r="B199" t="s">
+        <v>4</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A200">
+        <v>298</v>
+      </c>
+      <c r="B200" t="s">
+        <v>4</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A201">
+        <v>299</v>
+      </c>
+      <c r="B201" t="s">
+        <v>4</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A202">
+        <v>300</v>
+      </c>
+      <c r="B202" t="s">
+        <v>4</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A203">
+        <v>301</v>
+      </c>
+      <c r="B203" t="s">
+        <v>4</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A204">
+        <v>302</v>
+      </c>
+      <c r="B204" t="s">
+        <v>4</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A205">
+        <v>303</v>
+      </c>
+      <c r="B205" t="s">
+        <v>4</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A206">
+        <v>304</v>
+      </c>
+      <c r="B206" t="s">
+        <v>4</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A207">
+        <v>305</v>
+      </c>
+      <c r="B207" t="s">
+        <v>4</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A208">
+        <v>306</v>
+      </c>
+      <c r="B208" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A209">
+        <v>307</v>
+      </c>
+      <c r="B209" t="s">
+        <v>4</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A210">
+        <v>308</v>
+      </c>
+      <c r="B210" t="s">
+        <v>4</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A211">
+        <v>309</v>
+      </c>
+      <c r="B211" t="s">
+        <v>4</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A212">
+        <v>310</v>
+      </c>
+      <c r="B212" t="s">
+        <v>4</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A213">
+        <v>311</v>
+      </c>
+      <c r="B213" t="s">
+        <v>4</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A214">
+        <v>312</v>
+      </c>
+      <c r="B214" t="s">
+        <v>4</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A215">
+        <v>313</v>
+      </c>
+      <c r="B215" t="s">
+        <v>2</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A216">
+        <v>314</v>
+      </c>
+      <c r="B216" t="s">
+        <v>2</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A217">
+        <v>315</v>
+      </c>
+      <c r="B217" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A218">
+        <v>316</v>
+      </c>
+      <c r="B218" t="s">
+        <v>2</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A219">
+        <v>317</v>
+      </c>
+      <c r="B219" t="s">
+        <v>2</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A220">
+        <v>318</v>
+      </c>
+      <c r="B220" t="s">
+        <v>4</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A221">
+        <v>319</v>
+      </c>
+      <c r="B221" t="s">
+        <v>5</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A222">
+        <v>320</v>
+      </c>
+      <c r="B222" t="s">
+        <v>2</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A223">
+        <v>321</v>
+      </c>
+      <c r="B223" t="s">
+        <v>4</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A224">
+        <v>322</v>
+      </c>
+      <c r="B224" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A225">
+        <v>323</v>
+      </c>
+      <c r="B225" t="s">
+        <v>2</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A226">
+        <v>324</v>
+      </c>
+      <c r="B226" t="s">
+        <v>4</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A227">
+        <v>325</v>
+      </c>
+      <c r="B227" t="s">
+        <v>4</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A228">
+        <v>326</v>
+      </c>
+      <c r="B228" t="s">
+        <v>2</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A229">
+        <v>327</v>
+      </c>
+      <c r="B229" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A230">
+        <v>328</v>
+      </c>
+      <c r="B230" t="s">
+        <v>2</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A231">
+        <v>329</v>
+      </c>
+      <c r="B231" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A232">
+        <v>330</v>
+      </c>
+      <c r="B232" t="s">
+        <v>2</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A233">
+        <v>331</v>
+      </c>
+      <c r="B233" t="s">
+        <v>5</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A234">
+        <v>332</v>
+      </c>
+      <c r="B234" t="s">
+        <v>4</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A235">
+        <v>333</v>
+      </c>
+      <c r="B235" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A236">
+        <v>334</v>
+      </c>
+      <c r="B236" t="s">
+        <v>4</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A237">
+        <v>335</v>
+      </c>
+      <c r="B237" t="s">
+        <v>4</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A238">
+        <v>336</v>
+      </c>
+      <c r="B238" t="s">
+        <v>4</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A239">
+        <v>337</v>
+      </c>
+      <c r="B239" t="s">
+        <v>4</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A240">
+        <v>338</v>
+      </c>
+      <c r="B240" t="s">
+        <v>2</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A241">
+        <v>339</v>
+      </c>
+      <c r="B241" t="s">
+        <v>4</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A242">
+        <v>340</v>
+      </c>
+      <c r="B242" t="s">
+        <v>4</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A243">
+        <v>341</v>
+      </c>
+      <c r="B243" t="s">
+        <v>2</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A244">
+        <v>342</v>
+      </c>
+      <c r="B244" t="s">
+        <v>4</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A245">
+        <v>343</v>
+      </c>
+      <c r="B245" t="s">
+        <v>4</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A246">
+        <v>344</v>
+      </c>
+      <c r="B246" t="s">
+        <v>4</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A247">
+        <v>345</v>
+      </c>
+      <c r="B247" t="s">
+        <v>4</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A248">
+        <v>346</v>
+      </c>
+      <c r="B248" t="s">
+        <v>4</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A249">
+        <v>347</v>
+      </c>
+      <c r="B249" t="s">
+        <v>4</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A250">
+        <v>348</v>
+      </c>
+      <c r="B250" t="s">
+        <v>4</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A251">
+        <v>349</v>
+      </c>
+      <c r="B251" t="s">
+        <v>2</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A252">
+        <v>350</v>
+      </c>
+      <c r="B252" t="s">
+        <v>2</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A253">
+        <v>351</v>
+      </c>
+      <c r="B253" t="s">
+        <v>4</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A254">
+        <v>352</v>
+      </c>
+      <c r="B254" t="s">
+        <v>4</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A255">
+        <v>353</v>
+      </c>
+      <c r="B255" t="s">
+        <v>4</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A256">
+        <v>354</v>
+      </c>
+      <c r="B256" t="s">
+        <v>4</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A257">
+        <v>355</v>
+      </c>
+      <c r="B257" t="s">
+        <v>2</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A258">
+        <v>356</v>
+      </c>
+      <c r="B258" t="s">
+        <v>4</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A259">
+        <v>357</v>
+      </c>
+      <c r="B259" t="s">
+        <v>4</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A260">
+        <v>358</v>
+      </c>
+      <c r="B260" t="s">
+        <v>4</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A261">
+        <v>359</v>
+      </c>
+      <c r="B261" t="s">
+        <v>4</v>
+      </c>
+      <c r="C261" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A262">
+        <v>360</v>
+      </c>
+      <c r="B262" t="s">
+        <v>4</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A263">
+        <v>361</v>
+      </c>
+      <c r="B263" t="s">
+        <v>4</v>
+      </c>
+      <c r="C263" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A264">
+        <v>362</v>
+      </c>
+      <c r="B264" t="s">
+        <v>4</v>
+      </c>
+      <c r="C264" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A265">
+        <v>363</v>
+      </c>
+      <c r="B265" t="s">
+        <v>4</v>
+      </c>
+      <c r="C265" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A266">
+        <v>364</v>
+      </c>
+      <c r="B266" t="s">
+        <v>4</v>
+      </c>
+      <c r="C266" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A267">
+        <v>365</v>
+      </c>
+      <c r="B267" t="s">
+        <v>2</v>
+      </c>
+      <c r="C267" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A268">
+        <v>366</v>
+      </c>
+      <c r="B268" t="s">
+        <v>4</v>
+      </c>
+      <c r="C268" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A269">
+        <v>367</v>
+      </c>
+      <c r="B269" t="s">
+        <v>4</v>
+      </c>
+      <c r="C269" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A270">
+        <v>368</v>
+      </c>
+      <c r="B270" t="s">
+        <v>4</v>
+      </c>
+      <c r="C270" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A271">
+        <v>369</v>
+      </c>
+      <c r="B271" t="s">
+        <v>4</v>
+      </c>
+      <c r="C271" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A272">
+        <v>370</v>
+      </c>
+      <c r="B272" t="s">
+        <v>2</v>
+      </c>
+      <c r="C272" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A273">
+        <v>371</v>
+      </c>
+      <c r="B273" t="s">
+        <v>4</v>
+      </c>
+      <c r="C273" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A274">
+        <v>372</v>
+      </c>
+      <c r="B274" t="s">
+        <v>4</v>
+      </c>
+      <c r="C274" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A275">
+        <v>373</v>
+      </c>
+      <c r="B275" t="s">
+        <v>2</v>
+      </c>
+      <c r="C275" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A276">
+        <v>374</v>
+      </c>
+      <c r="B276" t="s">
+        <v>4</v>
+      </c>
+      <c r="C276" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A277">
+        <v>375</v>
+      </c>
+      <c r="B277" t="s">
+        <v>4</v>
+      </c>
+      <c r="C277" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A278">
+        <v>376</v>
+      </c>
+      <c r="B278" t="s">
+        <v>4</v>
+      </c>
+      <c r="C278" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A279">
+        <v>377</v>
+      </c>
+      <c r="B279" t="s">
+        <v>4</v>
+      </c>
+      <c r="C279" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A280">
+        <v>378</v>
+      </c>
+      <c r="B280" t="s">
+        <v>4</v>
+      </c>
+      <c r="C280" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A281">
+        <v>379</v>
+      </c>
+      <c r="B281" t="s">
+        <v>4</v>
+      </c>
+      <c r="C281" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A282">
+        <v>380</v>
+      </c>
+      <c r="B282" t="s">
+        <v>4</v>
+      </c>
+      <c r="C282" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A283">
+        <v>381</v>
+      </c>
+      <c r="B283" t="s">
+        <v>4</v>
+      </c>
+      <c r="C283" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A284">
+        <v>382</v>
+      </c>
+      <c r="B284" t="s">
+        <v>4</v>
+      </c>
+      <c r="C284" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A285">
+        <v>383</v>
+      </c>
+      <c r="B285" t="s">
+        <v>4</v>
+      </c>
+      <c r="C285" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A286">
+        <v>384</v>
+      </c>
+      <c r="B286" t="s">
+        <v>4</v>
+      </c>
+      <c r="C286" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A287">
+        <v>385</v>
+      </c>
+      <c r="B287" t="s">
+        <v>4</v>
+      </c>
+      <c r="C287" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A288">
+        <v>386</v>
+      </c>
+      <c r="B288" t="s">
+        <v>2</v>
+      </c>
+      <c r="C288" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A289">
+        <v>387</v>
+      </c>
+      <c r="B289" t="s">
+        <v>4</v>
+      </c>
+      <c r="C289" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A290">
+        <v>388</v>
+      </c>
+      <c r="B290" t="s">
+        <v>4</v>
+      </c>
+      <c r="C290" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A291">
+        <v>389</v>
+      </c>
+      <c r="B291" t="s">
+        <v>4</v>
+      </c>
+      <c r="C291" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A292">
+        <v>390</v>
+      </c>
+      <c r="B292" t="s">
+        <v>4</v>
+      </c>
+      <c r="C292" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A293">
+        <v>391</v>
+      </c>
+      <c r="B293" t="s">
+        <v>4</v>
+      </c>
+      <c r="C293" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A294">
+        <v>392</v>
+      </c>
+      <c r="B294" t="s">
+        <v>4</v>
+      </c>
+      <c r="C294" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A295">
+        <v>393</v>
+      </c>
+      <c r="B295" t="s">
+        <v>4</v>
+      </c>
+      <c r="C295" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A296">
+        <v>394</v>
+      </c>
+      <c r="B296" t="s">
+        <v>4</v>
+      </c>
+      <c r="C296" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A297">
+        <v>395</v>
+      </c>
+      <c r="B297" t="s">
+        <v>4</v>
+      </c>
+      <c r="C297" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A298">
+        <v>396</v>
+      </c>
+      <c r="B298" t="s">
+        <v>4</v>
+      </c>
+      <c r="C298" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A299">
+        <v>397</v>
+      </c>
+      <c r="B299" t="s">
+        <v>4</v>
+      </c>
+      <c r="C299" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A300">
+        <v>398</v>
+      </c>
+      <c r="B300" t="s">
+        <v>4</v>
+      </c>
+      <c r="C300" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A301">
+        <v>399</v>
+      </c>
+      <c r="B301" t="s">
+        <v>4</v>
+      </c>
+      <c r="C301" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A302">
+        <v>400</v>
+      </c>
+      <c r="B302" t="s">
+        <v>4</v>
+      </c>
+      <c r="C302" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A303">
+        <v>401</v>
+      </c>
+      <c r="B303" t="s">
+        <v>4</v>
+      </c>
+      <c r="C303" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A304">
+        <v>402</v>
+      </c>
+      <c r="B304" t="s">
+        <v>4</v>
+      </c>
+      <c r="C304" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A305">
+        <v>403</v>
+      </c>
+      <c r="B305" t="s">
+        <v>4</v>
+      </c>
+      <c r="C305" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A306">
+        <v>404</v>
+      </c>
+      <c r="B306" t="s">
+        <v>4</v>
+      </c>
+      <c r="C306" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A307">
+        <v>405</v>
+      </c>
+      <c r="B307" t="s">
+        <v>2</v>
+      </c>
+      <c r="C307" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A308">
+        <v>406</v>
+      </c>
+      <c r="B308" t="s">
+        <v>4</v>
+      </c>
+      <c r="C308" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A309">
+        <v>407</v>
+      </c>
+      <c r="B309" t="s">
+        <v>4</v>
+      </c>
+      <c r="C309" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A310">
+        <v>408</v>
+      </c>
+      <c r="B310" t="s">
+        <v>4</v>
+      </c>
+      <c r="C310" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A311">
+        <v>409</v>
+      </c>
+      <c r="B311" t="s">
+        <v>4</v>
+      </c>
+      <c r="C311" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A312">
+        <v>410</v>
+      </c>
+      <c r="B312" t="s">
+        <v>4</v>
+      </c>
+      <c r="C312" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A313">
+        <v>411</v>
+      </c>
+      <c r="B313" t="s">
+        <v>4</v>
+      </c>
+      <c r="C313" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A314">
+        <v>412</v>
+      </c>
+      <c r="B314" t="s">
+        <v>4</v>
+      </c>
+      <c r="C314" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A315">
+        <v>413</v>
+      </c>
+      <c r="B315" t="s">
+        <v>4</v>
+      </c>
+      <c r="C315" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A316">
+        <v>414</v>
+      </c>
+      <c r="B316" t="s">
+        <v>4</v>
+      </c>
+      <c r="C316" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A317">
+        <v>415</v>
+      </c>
+      <c r="B317" t="s">
+        <v>4</v>
+      </c>
+      <c r="C317" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A318">
+        <v>416</v>
+      </c>
+      <c r="B318" t="s">
+        <v>4</v>
+      </c>
+      <c r="C318" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A319">
+        <v>417</v>
+      </c>
+      <c r="B319" t="s">
+        <v>4</v>
+      </c>
+      <c r="C319" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A320">
+        <v>418</v>
+      </c>
+      <c r="B320" t="s">
+        <v>4</v>
+      </c>
+      <c r="C320" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A321">
+        <v>419</v>
+      </c>
+      <c r="B321" t="s">
+        <v>4</v>
+      </c>
+      <c r="C321" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A322">
+        <v>420</v>
+      </c>
+      <c r="B322" t="s">
+        <v>4</v>
+      </c>
+      <c r="C322" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A323">
+        <v>421</v>
+      </c>
+      <c r="B323" t="s">
+        <v>4</v>
+      </c>
+      <c r="C323" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A324">
+        <v>422</v>
+      </c>
+      <c r="B324" t="s">
+        <v>4</v>
+      </c>
+      <c r="C324" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A325">
+        <v>423</v>
+      </c>
+      <c r="B325" t="s">
+        <v>4</v>
+      </c>
+      <c r="C325" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A326">
+        <v>424</v>
+      </c>
+      <c r="B326" t="s">
+        <v>4</v>
+      </c>
+      <c r="C326" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A327">
+        <v>425</v>
+      </c>
+      <c r="B327" t="s">
+        <v>2</v>
+      </c>
+      <c r="C327" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A328">
+        <v>426</v>
+      </c>
+      <c r="B328" t="s">
+        <v>4</v>
+      </c>
+      <c r="C328" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A329">
+        <v>427</v>
+      </c>
+      <c r="B329" t="s">
+        <v>4</v>
+      </c>
+      <c r="C329" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A330">
+        <v>428</v>
+      </c>
+      <c r="B330" t="s">
+        <v>4</v>
+      </c>
+      <c r="C330" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A331">
+        <v>429</v>
+      </c>
+      <c r="B331" t="s">
+        <v>4</v>
+      </c>
+      <c r="C331" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A332">
+        <v>430</v>
+      </c>
+      <c r="B332" t="s">
+        <v>2</v>
+      </c>
+      <c r="C332" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A333">
+        <v>431</v>
+      </c>
+      <c r="B333" t="s">
+        <v>4</v>
+      </c>
+      <c r="C333" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A334">
+        <v>432</v>
+      </c>
+      <c r="B334" t="s">
+        <v>4</v>
+      </c>
+      <c r="C334" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A335">
+        <v>433</v>
+      </c>
+      <c r="B335" t="s">
+        <v>2</v>
+      </c>
+      <c r="C335" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A336">
+        <v>434</v>
+      </c>
+      <c r="B336" t="s">
+        <v>2</v>
+      </c>
+      <c r="C336" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A337">
+        <v>435</v>
+      </c>
+      <c r="B337" t="s">
+        <v>4</v>
+      </c>
+      <c r="C337" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A338">
+        <v>436</v>
+      </c>
+      <c r="B338" t="s">
+        <v>4</v>
+      </c>
+      <c r="C338" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A339">
+        <v>437</v>
+      </c>
+      <c r="B339" t="s">
+        <v>2</v>
+      </c>
+      <c r="C339" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A340">
+        <v>438</v>
+      </c>
+      <c r="B340" t="s">
+        <v>4</v>
+      </c>
+      <c r="C340" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A341">
+        <v>439</v>
+      </c>
+      <c r="B341" t="s">
+        <v>4</v>
+      </c>
+      <c r="C341" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A342">
+        <v>440</v>
+      </c>
+      <c r="B342" t="s">
+        <v>4</v>
+      </c>
+      <c r="C342" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A343">
+        <v>441</v>
+      </c>
+      <c r="B343" t="s">
+        <v>2</v>
+      </c>
+      <c r="C343" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A344">
+        <v>442</v>
+      </c>
+      <c r="B344" t="s">
+        <v>4</v>
+      </c>
+      <c r="C344" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A345">
+        <v>443</v>
+      </c>
+      <c r="B345" t="s">
+        <v>4</v>
+      </c>
+      <c r="C345" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A346">
+        <v>444</v>
+      </c>
+      <c r="B346" t="s">
+        <v>4</v>
+      </c>
+      <c r="C346" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A347">
+        <v>445</v>
+      </c>
+      <c r="B347" t="s">
+        <v>4</v>
+      </c>
+      <c r="C347" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A348">
+        <v>446</v>
+      </c>
+      <c r="B348" t="s">
+        <v>4</v>
+      </c>
+      <c r="C348" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A349">
+        <v>447</v>
+      </c>
+      <c r="B349" t="s">
+        <v>2</v>
+      </c>
+      <c r="C349" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A350">
+        <v>448</v>
+      </c>
+      <c r="B350" t="s">
+        <v>4</v>
+      </c>
+      <c r="C350" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A351">
+        <v>449</v>
+      </c>
+      <c r="B351" t="s">
+        <v>2</v>
+      </c>
+      <c r="C351" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A352">
+        <v>450</v>
+      </c>
+      <c r="B352" t="s">
+        <v>4</v>
+      </c>
+      <c r="C352" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A353">
+        <v>451</v>
+      </c>
+      <c r="B353" t="s">
+        <v>2</v>
+      </c>
+      <c r="C353" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A354">
+        <v>452</v>
+      </c>
+      <c r="B354" t="s">
+        <v>4</v>
+      </c>
+      <c r="C354" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A355">
+        <v>453</v>
+      </c>
+      <c r="B355" t="s">
+        <v>2</v>
+      </c>
+      <c r="C355" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A356">
+        <v>454</v>
+      </c>
+      <c r="B356" t="s">
+        <v>4</v>
+      </c>
+      <c r="C356" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A357">
+        <v>455</v>
+      </c>
+      <c r="B357" t="s">
+        <v>4</v>
+      </c>
+      <c r="C357" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A358">
+        <v>456</v>
+      </c>
+      <c r="B358" t="s">
+        <v>4</v>
+      </c>
+      <c r="C358" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A359">
+        <v>457</v>
+      </c>
+      <c r="B359" t="s">
+        <v>4</v>
+      </c>
+      <c r="C359" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A360">
+        <v>458</v>
+      </c>
+      <c r="B360" t="s">
+        <v>4</v>
+      </c>
+      <c r="C360" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A361">
+        <v>459</v>
+      </c>
+      <c r="B361" t="s">
+        <v>4</v>
+      </c>
+      <c r="C361" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A362">
+        <v>460</v>
+      </c>
+      <c r="B362" t="s">
+        <v>4</v>
+      </c>
+      <c r="C362" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A363">
+        <v>461</v>
+      </c>
+      <c r="B363" t="s">
+        <v>2</v>
+      </c>
+      <c r="C363" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A364">
+        <v>462</v>
+      </c>
+      <c r="B364" t="s">
+        <v>4</v>
+      </c>
+      <c r="C364" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A365">
+        <v>463</v>
+      </c>
+      <c r="B365" t="s">
+        <v>2</v>
+      </c>
+      <c r="C365" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A366">
+        <v>464</v>
+      </c>
+      <c r="B366" t="s">
+        <v>4</v>
+      </c>
+      <c r="C366" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A367">
+        <v>465</v>
+      </c>
+      <c r="B367" t="s">
+        <v>2</v>
+      </c>
+      <c r="C367" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A368">
+        <v>466</v>
+      </c>
+      <c r="B368" t="s">
+        <v>2</v>
+      </c>
+      <c r="C368" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A369">
+        <v>467</v>
+      </c>
+      <c r="B369" t="s">
+        <v>4</v>
+      </c>
+      <c r="C369" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A370">
+        <v>468</v>
+      </c>
+      <c r="B370" t="s">
+        <v>4</v>
+      </c>
+      <c r="C370" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A371">
+        <v>469</v>
+      </c>
+      <c r="B371" t="s">
+        <v>4</v>
+      </c>
+      <c r="C371" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A372">
+        <v>470</v>
+      </c>
+      <c r="B372" t="s">
+        <v>4</v>
+      </c>
+      <c r="C372" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A373">
+        <v>471</v>
+      </c>
+      <c r="B373" t="s">
+        <v>4</v>
+      </c>
+      <c r="C373" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A374">
+        <v>472</v>
+      </c>
+      <c r="B374" t="s">
+        <v>4</v>
+      </c>
+      <c r="C374" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A375">
+        <v>473</v>
+      </c>
+      <c r="B375" t="s">
+        <v>2</v>
+      </c>
+      <c r="C375" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A376">
+        <v>474</v>
+      </c>
+      <c r="B376" t="s">
+        <v>4</v>
+      </c>
+      <c r="C376" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A377">
+        <v>475</v>
+      </c>
+      <c r="B377" t="s">
+        <v>2</v>
+      </c>
+      <c r="C377" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A378">
+        <v>476</v>
+      </c>
+      <c r="B378" t="s">
+        <v>2</v>
+      </c>
+      <c r="C378" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A379">
+        <v>477</v>
+      </c>
+      <c r="B379" t="s">
+        <v>4</v>
+      </c>
+      <c r="C379" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A380">
+        <v>478</v>
+      </c>
+      <c r="B380" t="s">
+        <v>2</v>
+      </c>
+      <c r="C380" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A381">
+        <v>479</v>
+      </c>
+      <c r="B381" t="s">
+        <v>2</v>
+      </c>
+      <c r="C381" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A382">
+        <v>480</v>
+      </c>
+      <c r="B382" t="s">
+        <v>4</v>
+      </c>
+      <c r="C382" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A383">
+        <v>481</v>
+      </c>
+      <c r="B383" t="s">
+        <v>2</v>
+      </c>
+      <c r="C383" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A384">
+        <v>482</v>
+      </c>
+      <c r="B384" t="s">
+        <v>2</v>
+      </c>
+      <c r="C384" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A385">
+        <v>483</v>
+      </c>
+      <c r="B385" t="s">
+        <v>4</v>
+      </c>
+      <c r="C385" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A386">
+        <v>484</v>
+      </c>
+      <c r="B386" t="s">
+        <v>4</v>
+      </c>
+      <c r="C386" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A387">
+        <v>485</v>
+      </c>
+      <c r="B387" t="s">
+        <v>4</v>
+      </c>
+      <c r="C387" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A388">
+        <v>486</v>
+      </c>
+      <c r="B388" t="s">
+        <v>4</v>
+      </c>
+      <c r="C388" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A389">
+        <v>487</v>
+      </c>
+      <c r="B389" t="s">
+        <v>2</v>
+      </c>
+      <c r="C389" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A390">
+        <v>488</v>
+      </c>
+      <c r="B390" t="s">
+        <v>2</v>
+      </c>
+      <c r="C390" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A391">
+        <v>489</v>
+      </c>
+      <c r="B391" t="s">
+        <v>4</v>
+      </c>
+      <c r="C391" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A392">
+        <v>490</v>
+      </c>
+      <c r="B392" t="s">
+        <v>4</v>
+      </c>
+      <c r="C392" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A393">
+        <v>491</v>
+      </c>
+      <c r="B393" t="s">
+        <v>4</v>
+      </c>
+      <c r="C393" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A394">
+        <v>492</v>
+      </c>
+      <c r="B394" t="s">
+        <v>4</v>
+      </c>
+      <c r="C394" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A395">
+        <v>493</v>
+      </c>
+      <c r="B395" t="s">
+        <v>4</v>
+      </c>
+      <c r="C395" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A396">
+        <v>494</v>
+      </c>
+      <c r="B396" t="s">
+        <v>2</v>
+      </c>
+      <c r="C396" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A397">
+        <v>495</v>
+      </c>
+      <c r="B397" t="s">
+        <v>2</v>
+      </c>
+      <c r="C397" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A398">
+        <v>496</v>
+      </c>
+      <c r="B398" t="s">
+        <v>4</v>
+      </c>
+      <c r="C398" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A399">
+        <v>497</v>
+      </c>
+      <c r="B399" t="s">
+        <v>2</v>
+      </c>
+      <c r="C399" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A400">
+        <v>498</v>
+      </c>
+      <c r="B400" t="s">
+        <v>4</v>
+      </c>
+      <c r="C400" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C1" xr:uid="{7034A0F2-F044-457F-8383-77C15214A3A3}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C400">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
+  <conditionalFormatting sqref="C241:C279 C281:C359">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/coincidencias_comisiones.xlsx
+++ b/coincidencias_comisiones.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vicel\Proyectos\constitutional-proposal-tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E811FBC0-36C5-4AD8-AD87-95C95CE040EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B765E9D-078A-40C9-BC8F-8964DEFCD388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" activeTab="1" xr2:uid="{EB1ABC4A-685D-416C-81A4-F83CAA4FCE57}"/>
+    <workbookView xWindow="1900" yWindow="830" windowWidth="17680" windowHeight="12850" xr2:uid="{EB1ABC4A-685D-416C-81A4-F83CAA4FCE57}"/>
   </bookViews>
   <sheets>
     <sheet name="Comisión 1" sheetId="1" r:id="rId1"/>
